--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -860,13 +860,13 @@
         <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="H2" t="n">
         <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="J2" t="n">
         <v>1.04</v>
@@ -908,7 +908,7 @@
         <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 00:29:56</t>
+          <t>2026-06-02 02:36:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G2" t="n">
         <v>970</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I2" t="n">
         <v>970</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 02:36:39</t>
+          <t>2026-06-02 04:43:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 04:43:26</t>
+          <t>2026-06-02 06:50:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -881,22 +881,22 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.27</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P2" t="n">
         <v>1.27</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="R2" t="n">
         <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 06:50:15</t>
+          <t>2026-06-02 08:57:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,7 +1080,261 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 08:57:22</t>
+          <t>2026-06-02 11:04:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AFC Eskilstuna</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Karlbergs BK</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K3" t="n">
+        <v>950</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-06-02 11:04:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 11:04:34</t>
+          <t>2026-06-02 13:11:30</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 11:04:34</t>
+          <t>2026-06-02 13:11:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>3.45</v>
+        <v>1.27</v>
       </c>
       <c r="O2" t="n">
         <v>1.21</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 13:11:30</t>
+          <t>2026-06-02 15:18:07</t>
         </is>
       </c>
     </row>
@@ -1129,212 +1129,212 @@
         <v>950</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 13:11:30</t>
+          <t>2026-06-02 15:18:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.27</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
         <v>1.21</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 15:18:07</t>
+          <t>2026-06-02 17:24:55</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1135,16 +1135,16 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O3" t="n">
         <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 15:18:07</t>
+          <t>2026-06-02 17:24:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>3.45</v>
+        <v>1.27</v>
       </c>
       <c r="O2" t="n">
         <v>1.21</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 17:24:55</t>
+          <t>2026-06-02 19:31:39</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O3" t="n">
         <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q3" t="n">
         <v>1.15</v>
@@ -1159,10 +1159,10 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 17:24:55</t>
+          <t>2026-06-02 19:31:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 19:31:39</t>
+          <t>2026-06-02 21:38:14</t>
         </is>
       </c>
     </row>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O3" t="n">
         <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q3" t="n">
         <v>1.15</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 19:31:39</t>
+          <t>2026-06-02 21:38:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -869,7 +869,7 @@
         <v>970</v>
       </c>
       <c r="J2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -908,7 +908,7 @@
         <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 21:38:14</t>
+          <t>2026-06-02 23:44:49</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
         <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="H3" t="n">
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="J3" t="n">
         <v>1.04</v>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O3" t="n">
         <v>1.16</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 21:38:14</t>
+          <t>2026-06-02 23:44:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB3"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Finnish Kakkonen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,33 +843,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Laholms</t>
+          <t>Pepo</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hassleholms IF</t>
+          <t>Reipas</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -881,22 +881,22 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="P2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="R2" t="n">
         <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -905,7 +905,7 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 23:44:49</t>
+          <t>2026-06-03 01:51:31</t>
         </is>
       </c>
     </row>
@@ -1097,33 +1097,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AFC Eskilstuna</t>
+          <t>Laholms</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Karlbergs BK</t>
+          <t>Hassleholms IF</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G3" t="n">
         <v>970</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
         <v>970</v>
       </c>
       <c r="J3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1135,22 +1135,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="O3" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1162,179 +1162,433 @@
         <v>1.02</v>
       </c>
       <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-06-03 01:51:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AFC Eskilstuna</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Karlbergs BK</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G4" t="n">
+        <v>970</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I4" t="n">
+        <v>970</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K4" t="n">
+        <v>950</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V4" t="n">
         <v>1.02</v>
       </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>2026-06-02 23:44:49</t>
+      <c r="W4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-06-03 01:51:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Finnish Kakkonen</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -848,28 +848,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pepo</t>
+          <t>ES Ben Aknoun</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Reipas</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>2.2</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.83</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>1.86</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -884,19 +884,19 @@
         <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="R2" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="S2" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -908,7 +908,7 @@
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 01:51:31</t>
+          <t>2026-06-03 03:58:27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Finnish Kakkonen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,33 +1097,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Laholms</t>
+          <t>Pepo</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hassleholms IF</t>
+          <t>Reipas</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1135,22 +1135,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="O3" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="P3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1162,7 +1162,7 @@
         <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 01:51:31</t>
+          <t>2026-06-03 03:58:27</t>
         </is>
       </c>
     </row>
@@ -1351,17 +1351,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AFC Eskilstuna</t>
+          <t>Laholms</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Karlbergs BK</t>
+          <t>Hassleholms IF</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1371,13 +1371,13 @@
         <v>970</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I4" t="n">
         <v>970</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1389,22 +1389,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="O4" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="R4" t="n">
         <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1416,179 +1416,941 @@
         <v>1.02</v>
       </c>
       <c r="W4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-06-03 03:58:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AFC Eskilstuna</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Karlbergs BK</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G5" t="n">
+        <v>970</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I5" t="n">
+        <v>970</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K5" t="n">
+        <v>950</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V5" t="n">
         <v>1.02</v>
       </c>
-      <c r="X4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>2026-06-03 01:51:31</t>
+      <c r="W5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-06-03 03:58:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HUSA Agadir</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FUS Rabat</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-06-03 03:58:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FAR Rabat</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DHJ El Jadida</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I7" t="n">
+        <v>130</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K7" t="n">
+        <v>950</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-03 03:58:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.05</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>2.2</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83</v>
+        <v>3.45</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J2" t="n">
-        <v>1.86</v>
+        <v>2.6</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>95</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -890,13 +890,13 @@
         <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="R2" t="n">
         <v>1.12</v>
       </c>
       <c r="S2" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -905,73 +905,73 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W2" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AS2" t="n">
         <v>1.03</v>
@@ -980,43 +980,43 @@
         <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 03:58:27</t>
+          <t>2026-06-03 06:05:17</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
         <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H3" t="n">
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J3" t="n">
         <v>1.04</v>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="O3" t="n">
         <v>1.09</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 03:58:27</t>
+          <t>2026-06-03 06:05:17</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 03:58:27</t>
+          <t>2026-06-03 06:05:17</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="O5" t="n">
         <v>1.16</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 03:58:27</t>
+          <t>2026-06-03 06:05:17</t>
         </is>
       </c>
     </row>
@@ -1873,112 +1873,112 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="H6" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="I6" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="J6" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O6" t="n">
         <v>1.47</v>
       </c>
-      <c r="M6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.52</v>
-      </c>
       <c r="P6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V6" t="n">
         <v>1.53</v>
       </c>
-      <c r="Q6" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.57</v>
-      </c>
       <c r="W6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X6" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AA6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF6" t="n">
         <v>24</v>
       </c>
       <c r="AG6" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
         <v>30</v>
       </c>
       <c r="AI6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL6" t="n">
         <v>80</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AO6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP6" t="n">
         <v>1.01</v>
@@ -2035,68 +2035,68 @@
         <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.69</v>
+        <v>3.05</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
         <v>1.04</v>
       </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>1.08</v>
-      </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 03:58:27</t>
+          <t>2026-06-03 06:05:17</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>1.22</v>
       </c>
       <c r="G7" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="H7" t="n">
         <v>1.04</v>
@@ -2139,19 +2139,19 @@
         <v>130</v>
       </c>
       <c r="J7" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
       </c>
       <c r="L7" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="n">
         <v>1.26</v>
@@ -2166,7 +2166,7 @@
         <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
         <v>2.54</v>
@@ -2181,7 +2181,7 @@
         <v>4.1</v>
       </c>
       <c r="X7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y7" t="n">
         <v>55</v>
@@ -2193,10 +2193,10 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -2205,10 +2205,10 @@
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
         <v>60</v>
@@ -2217,10 +2217,10 @@
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AK7" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AL7" t="n">
         <v>75</v>
@@ -2229,7 +2229,7 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>6.2</v>
+        <v>970</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
@@ -2241,10 +2241,10 @@
         <v>4.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.9</v>
+        <v>2.36</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AT7" t="n">
         <v>3.2</v>
@@ -2253,22 +2253,22 @@
         <v>4</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.68</v>
+        <v>2.36</v>
       </c>
       <c r="AX7" t="n">
         <v>3.1</v>
       </c>
       <c r="AY7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>3.8</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BA7" t="n">
-        <v>2.66</v>
+        <v>2.36</v>
       </c>
       <c r="BB7" t="n">
         <v>3.45</v>
@@ -2277,58 +2277,58 @@
         <v>4.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.68</v>
+        <v>2.36</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2346,11 +2346,11 @@
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-03 03:58:27</t>
+          <t>2026-06-03 06:05:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Finnish Kakkonen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,36 +843,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ES Ben Aknoun</t>
+          <t>AIFK Turku</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Pallo-Iirot</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="K2" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -884,19 +884,19 @@
         <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="P2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.12</v>
-      </c>
       <c r="S2" t="n">
-        <v>1.45</v>
+        <v>1.08</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -905,118 +905,118 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>490</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>390</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 06:05:17</t>
+          <t>2026-06-03 08:12:38</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Finnish Kakkonen</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1102,246 +1102,246 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Pepo</t>
+          <t>ES Ben Aknoun</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Reipas</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.85</v>
       </c>
       <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO3" t="n">
         <v>110</v>
       </c>
-      <c r="H3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I3" t="n">
-        <v>110</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="K3" t="n">
-        <v>950</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>28</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 06:05:17</t>
+          <t>2026-06-03 08:12:38</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Finnish Kakkonen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,17 +1351,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Laholms</t>
+          <t>Pepo</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hassleholms IF</t>
+          <t>Reipas</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1371,13 +1371,13 @@
         <v>970</v>
       </c>
       <c r="H4" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
         <v>970</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1389,22 +1389,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="O4" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="P4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="R4" t="n">
         <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1416,7 +1416,7 @@
         <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 06:05:17</t>
+          <t>2026-06-03 08:12:38</t>
         </is>
       </c>
     </row>
@@ -1605,21 +1605,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AFC Eskilstuna</t>
+          <t>Laholms</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Karlbergs BK</t>
+          <t>Hassleholms IF</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="G5" t="n">
         <v>970</v>
@@ -1628,10 +1628,10 @@
         <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>970</v>
+        <v>1.79</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="O5" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.15</v>
+        <v>1.59</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>1.16</v>
+        <v>1.72</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>2.16</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 06:05:17</t>
+          <t>2026-06-03 08:12:38</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,159 +1859,159 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HUSA Agadir</t>
+          <t>AFC Eskilstuna</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Karlbergs BK</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7</v>
+        <v>970</v>
       </c>
       <c r="H6" t="n">
-        <v>2.56</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1</v>
+        <v>970</v>
       </c>
       <c r="J6" t="n">
-        <v>2.66</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>1.32</v>
       </c>
       <c r="O6" t="n">
-        <v>1.47</v>
+        <v>1.16</v>
       </c>
       <c r="P6" t="n">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.32</v>
+        <v>1.15</v>
       </c>
       <c r="R6" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>3.95</v>
+        <v>1.16</v>
       </c>
       <c r="T6" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.53</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
         <v>1.03</v>
@@ -2020,7 +2020,7 @@
         <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
         <v>1.03</v>
@@ -2035,46 +2035,46 @@
         <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
@@ -2086,17 +2086,17 @@
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 06:05:17</t>
+          <t>2026-06-03 08:12:38</t>
         </is>
       </c>
     </row>
@@ -2113,84 +2113,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>HUSA Agadir</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DHJ El Jadida</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.22</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>1.29</v>
+        <v>3.75</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="I7" t="n">
-        <v>130</v>
+        <v>3.05</v>
       </c>
       <c r="J7" t="n">
-        <v>4.6</v>
+        <v>2.92</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>3.35</v>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="P7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T7" t="n">
         <v>1.94</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.54</v>
-      </c>
       <c r="U7" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="V7" t="n">
-        <v>1.04</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="X7" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>55</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB7" t="n">
         <v>970</v>
@@ -2199,158 +2199,412 @@
         <v>970</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AG7" t="n">
         <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BH7" t="n">
         <v>970</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="BI7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:12:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FAR Rabat</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>DHJ El Jadida</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I8" t="n">
+        <v>130</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>950</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X8" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
         <v>970</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AC8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL8" t="n">
         <v>75</v>
       </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
         <v>970</v>
       </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AQ8" t="n">
         <v>4.8</v>
       </c>
-      <c r="AR7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV7" t="n">
+      <c r="AR8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT8" t="n">
         <v>3.25</v>
       </c>
-      <c r="AW7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AY7" t="n">
+      <c r="AU8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AY8" t="n">
         <v>3.85</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="AZ8" t="n">
         <v>3.8</v>
       </c>
-      <c r="BA7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>13</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>22</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>10</v>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-06-03 06:05:17</t>
+      <c r="BA8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:12:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -860,19 +860,19 @@
         <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H2" t="n">
         <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="O2" t="n">
         <v>1.08</v>
@@ -890,7 +890,7 @@
         <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="R2" t="n">
         <v>1.24</v>
@@ -965,52 +965,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 08:12:38</t>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
@@ -1120,73 +1120,73 @@
         <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="P3" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="R3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="V3" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
         <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y3" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA3" t="n">
         <v>130</v>
       </c>
       <c r="AB3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AF3" t="n">
         <v>11.5</v>
@@ -1195,146 +1195,146 @@
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AJ3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM3" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN3" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AO3" t="n">
         <v>110</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR3" t="n">
-        <v>28</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AU3" t="n">
         <v>7.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
       <c r="AY3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>7.2</v>
+        <v>18.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.4</v>
+        <v>60</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.2</v>
+        <v>19</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.2</v>
+        <v>19.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BE3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="BG3" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>15</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BH3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="BT3" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="BZ3" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.800000000000001</v>
+        <v>19</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 08:12:38</t>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>970</v>
       </c>
       <c r="J4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 08:12:38</t>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>
@@ -1619,160 +1619,160 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="G5" t="n">
-        <v>970</v>
+        <v>6.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="I5" t="n">
         <v>1.79</v>
       </c>
       <c r="J5" t="n">
-        <v>1.09</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>1.27</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
         <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>1.27</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.72</v>
+        <v>2.56</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V5" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1781,13 +1781,13 @@
         <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI5" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK5" t="n">
         <v>1.01</v>
@@ -1799,13 +1799,13 @@
         <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO5" t="n">
         <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BQ5" t="n">
         <v>1.01</v>
@@ -1817,32 +1817,32 @@
         <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BU5" t="n">
         <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BW5" t="n">
         <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY5" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA5" t="n">
         <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 08:12:38</t>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>
@@ -1873,160 +1873,160 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="G6" t="n">
-        <v>970</v>
+        <v>3.05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="I6" t="n">
-        <v>970</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>2.74</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M6" t="n">
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.32</v>
+        <v>3.45</v>
       </c>
       <c r="O6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.15</v>
+        <v>1.51</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="S6" t="n">
-        <v>1.16</v>
+        <v>2.14</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.49</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -2035,13 +2035,13 @@
         <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI6" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK6" t="n">
         <v>1.01</v>
@@ -2053,50 +2053,50 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO6" t="n">
         <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ6" t="n">
         <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS6" t="n">
         <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU6" t="n">
         <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW6" t="n">
         <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY6" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA6" t="n">
         <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 08:12:38</t>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>
@@ -2130,16 +2130,16 @@
         <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="H7" t="n">
         <v>2.56</v>
       </c>
       <c r="I7" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="J7" t="n">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="K7" t="n">
         <v>3.35</v>
@@ -2151,7 +2151,7 @@
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O7" t="n">
         <v>1.45</v>
@@ -2160,25 +2160,25 @@
         <v>1.62</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="R7" t="n">
         <v>1.23</v>
       </c>
       <c r="S7" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V7" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -2190,7 +2190,7 @@
         <v>970</v>
       </c>
       <c r="AA7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB7" t="n">
         <v>970</v>
@@ -2205,13 +2205,13 @@
         <v>44</v>
       </c>
       <c r="AF7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG7" t="n">
         <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>70</v>
@@ -2235,61 +2235,61 @@
         <v>46</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.61</v>
+        <v>3.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.9</v>
+        <v>3.15</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.32</v>
+        <v>3.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.37</v>
+        <v>3.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.61</v>
+        <v>3.25</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.14</v>
+        <v>3.45</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.82</v>
+        <v>3.75</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.41</v>
+        <v>3.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.41</v>
+        <v>3.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.41</v>
+        <v>3.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.38</v>
+        <v>3.85</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.38</v>
+        <v>3.9</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.84</v>
+        <v>3.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.38</v>
+        <v>3.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.85</v>
+        <v>3.85</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.83</v>
+        <v>3.75</v>
       </c>
       <c r="BH7" t="n">
-        <v>970</v>
+        <v>5</v>
       </c>
       <c r="BI7" t="n">
         <v>2.4</v>
@@ -2298,37 +2298,37 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.09</v>
+        <v>5.9</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.73</v>
+        <v>4.5</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2340,17 +2340,17 @@
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-03 08:12:38</t>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>
@@ -2381,49 +2381,49 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="G8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="H8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>24</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O8" t="n">
         <v>1.29</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I8" t="n">
-        <v>130</v>
-      </c>
-      <c r="J8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>950</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.26</v>
       </c>
       <c r="P8" t="n">
         <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="R8" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="T8" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="U8" t="n">
         <v>1.5</v>
@@ -2435,10 +2435,10 @@
         <v>4.2</v>
       </c>
       <c r="X8" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="Y8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -2447,13 +2447,13 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="AC8" t="n">
         <v>970</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
@@ -2483,94 +2483,94 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>970</v>
+        <v>6.8</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU8" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR8" t="n">
+      <c r="AV8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW8" t="n">
         <v>3.1</v>
       </c>
-      <c r="AS8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.26</v>
-      </c>
       <c r="AX8" t="n">
-        <v>3.15</v>
+        <v>5.2</v>
       </c>
       <c r="AY8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BH8" t="n">
         <v>3.85</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BB8" t="n">
+      <c r="BI8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN8" t="n">
         <v>3.5</v>
       </c>
-      <c r="BC8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1000</v>
-      </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-03 08:12:38</t>
+          <t>2026-06-03 10:20:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -869,7 +869,7 @@
         <v>110</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -905,10 +905,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1022,65 +1022,65 @@
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -1111,25 +1111,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="H3" t="n">
         <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
@@ -1153,16 +1153,16 @@
         <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="U3" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="X3" t="n">
         <v>12</v>
@@ -1186,7 +1186,7 @@
         <v>19.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AF3" t="n">
         <v>11.5</v>
@@ -1204,7 +1204,7 @@
         <v>24</v>
       </c>
       <c r="AK3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL3" t="n">
         <v>50</v>
@@ -1225,10 +1225,10 @@
         <v>12</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT3" t="n">
         <v>6.6</v>
@@ -1240,7 +1240,7 @@
         <v>16</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="AX3" t="n">
         <v>9.6</v>
@@ -1273,68 +1273,68 @@
         <v>50</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BJ3" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="BP3" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BR3" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="BT3" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="BZ3" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>19</v>
+        <v>7.8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -1530,65 +1530,65 @@
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>1.79</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K5" t="n">
         <v>5</v>
@@ -1643,7 +1643,7 @@
         <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.21</v>
@@ -1655,16 +1655,16 @@
         <v>1.61</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="S5" t="n">
         <v>2.56</v>
       </c>
       <c r="T5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U5" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V5" t="n">
         <v>2.26</v>
@@ -1727,122 +1727,122 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BH5" t="n">
         <v>4.4</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BJ5" t="n">
         <v>10.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BN5" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP5" t="n">
         <v>46</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BT5" t="n">
         <v>4.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BV5" t="n">
         <v>12</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BX5" t="n">
         <v>25</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BZ5" t="n">
         <v>18</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
         <v>1.17</v>
       </c>
       <c r="P6" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="Q6" t="n">
         <v>1.51</v>
@@ -1912,7 +1912,7 @@
         <v>1.56</v>
       </c>
       <c r="S6" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="T6" t="n">
         <v>1.48</v>
@@ -1978,125 +1978,125 @@
         <v>16.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BH6" t="n">
         <v>4.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BN6" t="n">
         <v>6.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BP6" t="n">
         <v>19</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BR6" t="n">
         <v>27</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BT6" t="n">
         <v>7</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BV6" t="n">
         <v>21</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BX6" t="n">
         <v>28</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>17.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="G7" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="H7" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="I7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.25</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.35</v>
       </c>
       <c r="L7" t="n">
         <v>1.43</v>
@@ -2151,16 +2151,16 @@
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="O7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="R7" t="n">
         <v>1.23</v>
@@ -2175,10 +2175,10 @@
         <v>1.89</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W7" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -2205,7 +2205,7 @@
         <v>44</v>
       </c>
       <c r="AF7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG7" t="n">
         <v>970</v>
@@ -2217,76 +2217,76 @@
         <v>70</v>
       </c>
       <c r="AJ7" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK7" t="n">
         <v>55</v>
       </c>
       <c r="AL7" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>3.2</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>3.15</v>
-      </c>
       <c r="AR7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV7" t="n">
         <v>3.5</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="AW7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX7" t="n">
         <v>3.8</v>
       </c>
-      <c r="AT7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AY7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BH7" t="n">
         <v>5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>
@@ -2381,64 +2381,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="G8" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="H8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="I8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J8" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="K8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
         <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="V8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="X8" t="n">
         <v>970</v>
       </c>
       <c r="Y8" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -2453,7 +2453,7 @@
         <v>970</v>
       </c>
       <c r="AD8" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
@@ -2465,7 +2465,7 @@
         <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
@@ -2477,73 +2477,73 @@
         <v>970</v>
       </c>
       <c r="AL8" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.5</v>
+        <v>3.35</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AT8" t="n">
         <v>5.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY8" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="BB8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BE8" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI8" t="n">
         <v>3</v>
@@ -2561,16 +2561,16 @@
         <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-03 10:20:28</t>
+          <t>2026-06-03 12:28:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -857,160 +857,160 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="G2" t="n">
-        <v>110</v>
+        <v>1.99</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="I2" t="n">
-        <v>110</v>
+        <v>4.5</v>
       </c>
       <c r="J2" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>6.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>1.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
       <c r="R2" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="S2" t="n">
-        <v>1.08</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
         <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -1019,68 +1019,68 @@
         <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.02</v>
+        <v>3.3</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.02</v>
+        <v>4.4</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.02</v>
+        <v>3.4</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.02</v>
+        <v>5.1</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.02</v>
+        <v>6</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.02</v>
+        <v>4.3</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.02</v>
+        <v>2.24</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.02</v>
+        <v>2.26</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.02</v>
+        <v>5.1</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -1111,25 +1111,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="G3" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
@@ -1141,7 +1141,7 @@
         <v>1.41</v>
       </c>
       <c r="P3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q3" t="n">
         <v>2.18</v>
@@ -1156,19 +1156,19 @@
         <v>1.97</v>
       </c>
       <c r="U3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
         <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="X3" t="n">
         <v>12</v>
       </c>
       <c r="Y3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z3" t="n">
         <v>36</v>
@@ -1186,7 +1186,7 @@
         <v>19.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AF3" t="n">
         <v>11.5</v>
@@ -1198,7 +1198,7 @@
         <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AJ3" t="n">
         <v>24</v>
@@ -1207,16 +1207,16 @@
         <v>25</v>
       </c>
       <c r="AL3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM3" t="n">
         <v>160</v>
       </c>
       <c r="AN3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO3" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP3" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
         <v>16</v>
       </c>
       <c r="AW3" t="n">
-        <v>50</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX3" t="n">
         <v>9.6</v>
@@ -1276,7 +1276,7 @@
         <v>3.15</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.54</v>
+        <v>2.74</v>
       </c>
       <c r="BJ3" t="n">
         <v>11.5</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN3" t="n">
         <v>4.6</v>
@@ -1297,7 +1297,7 @@
         <v>3.6</v>
       </c>
       <c r="BP3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ3" t="n">
         <v>6.2</v>
@@ -1306,35 +1306,35 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT3" t="n">
         <v>8.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -1365,160 +1365,160 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="G4" t="n">
-        <v>970</v>
+        <v>2.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="I4" t="n">
-        <v>970</v>
+        <v>3.3</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.26</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>2.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.82</v>
       </c>
       <c r="S4" t="n">
-        <v>1.09</v>
+        <v>2.04</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.69</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1527,68 +1527,68 @@
         <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.02</v>
+        <v>3.45</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.02</v>
+        <v>4.6</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.02</v>
+        <v>8.6</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.02</v>
+        <v>3.8</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.02</v>
+        <v>5.9</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.02</v>
+        <v>6.6</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.02</v>
+        <v>4.1</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.02</v>
+        <v>6.6</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.02</v>
+        <v>7</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.02</v>
+        <v>5.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -1619,79 +1619,79 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="H5" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="I5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
         <v>4.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="R5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S5" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="T5" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="U5" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V5" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="W5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X5" t="n">
         <v>23</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA5" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AB5" t="n">
         <v>24</v>
       </c>
       <c r="AC5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD5" t="n">
         <v>11</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>11.5</v>
       </c>
       <c r="AE5" t="n">
         <v>18.5</v>
@@ -1703,7 +1703,7 @@
         <v>23</v>
       </c>
       <c r="AH5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI5" t="n">
         <v>34</v>
@@ -1712,7 +1712,7 @@
         <v>150</v>
       </c>
       <c r="AK5" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AL5" t="n">
         <v>75</v>
@@ -1721,128 +1721,128 @@
         <v>110</v>
       </c>
       <c r="AN5" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.7</v>
+        <v>16.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AR5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH5" t="n">
         <v>4.1</v>
       </c>
-      <c r="AS5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BI5" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="BJ5" t="n">
         <v>10.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BN5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="BP5" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BU5" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="BV5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BX5" t="n">
         <v>25</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BZ5" t="n">
         <v>18</v>
       </c>
       <c r="CA5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         <v>2.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R6" t="n">
         <v>1.56</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G7" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="K7" t="n">
         <v>3.25</v>
@@ -2175,10 +2175,10 @@
         <v>1.89</v>
       </c>
       <c r="V7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -2235,34 +2235,34 @@
         <v>48</v>
       </c>
       <c r="AP7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>3.25</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AR7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AS7" t="n">
         <v>4.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AU7" t="n">
         <v>5.3</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX7" t="n">
         <v>3.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AZ7" t="n">
         <v>3.8</v>
@@ -2289,7 +2289,7 @@
         <v>4.1</v>
       </c>
       <c r="BH7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BI7" t="n">
         <v>2.4</v>
@@ -2298,31 +2298,31 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
@@ -2340,17 +2340,17 @@
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.27</v>
       </c>
       <c r="G8" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="H8" t="n">
         <v>14</v>
@@ -2393,13 +2393,13 @@
         <v>21</v>
       </c>
       <c r="J8" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="K8" t="n">
         <v>6.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
@@ -2432,7 +2432,7 @@
         <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="X8" t="n">
         <v>970</v>
@@ -2483,7 +2483,7 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>6.6</v>
+        <v>970</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
@@ -2495,10 +2495,10 @@
         <v>5.7</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.35</v>
+        <v>2.46</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.4</v>
+        <v>1.84</v>
       </c>
       <c r="AT8" t="n">
         <v>5.4</v>
@@ -2507,10 +2507,10 @@
         <v>4.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.35</v>
+        <v>1.83</v>
       </c>
       <c r="AX8" t="n">
         <v>5.3</v>
@@ -2522,7 +2522,7 @@
         <v>5.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>3.35</v>
+        <v>1.83</v>
       </c>
       <c r="BB8" t="n">
         <v>7.2</v>
@@ -2531,34 +2531,34 @@
         <v>4.9</v>
       </c>
       <c r="BD8" t="n">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="BE8" t="n">
-        <v>3.35</v>
+        <v>1.83</v>
       </c>
       <c r="BF8" t="n">
         <v>4.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.4</v>
+        <v>1.84</v>
       </c>
       <c r="BH8" t="n">
         <v>3.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BN8" t="n">
         <v>3.55</v>
@@ -2576,35 +2576,35 @@
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-03 12:28:17</t>
+          <t>2026-06-03 14:36:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -860,22 +860,22 @@
         <v>1.76</v>
       </c>
       <c r="G2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="I2" t="n">
         <v>4.5</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
@@ -887,10 +887,10 @@
         <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="R2" t="n">
         <v>1.71</v>
@@ -905,16 +905,16 @@
         <v>2.62</v>
       </c>
       <c r="V2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X2" t="n">
         <v>40</v>
       </c>
       <c r="Y2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z2" t="n">
         <v>44</v>
@@ -965,58 +965,58 @@
         <v>27</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH2" t="n">
         <v>5.4</v>
@@ -1037,7 +1037,7 @@
         <v>1.33</v>
       </c>
       <c r="BN2" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
         <v>3.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 14:36:03</t>
+          <t>2026-06-03 16:43:36</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="G3" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="n">
         <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
         <v>1.47</v>
@@ -1138,7 +1138,7 @@
         <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P3" t="n">
         <v>1.69</v>
@@ -1150,19 +1150,19 @@
         <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
         <v>12</v>
@@ -1183,10 +1183,10 @@
         <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF3" t="n">
         <v>11.5</v>
@@ -1195,16 +1195,16 @@
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI3" t="n">
         <v>90</v>
       </c>
       <c r="AJ3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK3" t="n">
         <v>24</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>25</v>
       </c>
       <c r="AL3" t="n">
         <v>48</v>
@@ -1213,22 +1213,22 @@
         <v>160</v>
       </c>
       <c r="AN3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO3" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR3" t="n">
         <v>8</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT3" t="n">
         <v>6.6</v>
@@ -1237,22 +1237,22 @@
         <v>7.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.199999999999999</v>
+        <v>48</v>
       </c>
       <c r="AX3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>60</v>
+        <v>9.4</v>
       </c>
       <c r="BB3" t="n">
         <v>19</v>
@@ -1261,7 +1261,7 @@
         <v>19.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE3" t="n">
         <v>9.800000000000001</v>
@@ -1270,7 +1270,7 @@
         <v>14.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>50</v>
+        <v>9.6</v>
       </c>
       <c r="BH3" t="n">
         <v>3.15</v>
@@ -1282,59 +1282,59 @@
         <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>8.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA3" t="n">
         <v>8.4</v>
       </c>
-      <c r="BU3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 14:36:03</t>
+          <t>2026-06-03 16:43:36</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G4" t="n">
         <v>2.4</v>
@@ -1374,7 +1374,7 @@
         <v>2.8</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J4" t="n">
         <v>3.6</v>
@@ -1386,25 +1386,25 @@
         <v>1.2</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>1.02</v>
       </c>
       <c r="O4" t="n">
         <v>1.14</v>
       </c>
       <c r="P4" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R4" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="S4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T4" t="n">
         <v>1.44</v>
@@ -1416,7 +1416,7 @@
         <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="X4" t="n">
         <v>42</v>
@@ -1473,58 +1473,58 @@
         <v>18</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BH4" t="n">
         <v>5.3</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 14:36:03</t>
+          <t>2026-06-03 16:43:36</t>
         </is>
       </c>
     </row>
@@ -1622,19 +1622,19 @@
         <v>4.8</v>
       </c>
       <c r="G5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="H5" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="J5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L5" t="n">
         <v>1.28</v>
@@ -1646,13 +1646,13 @@
         <v>4.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
         <v>2.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R5" t="n">
         <v>1.46</v>
@@ -1661,16 +1661,16 @@
         <v>2.72</v>
       </c>
       <c r="T5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U5" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="V5" t="n">
         <v>2.22</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X5" t="n">
         <v>23</v>
@@ -1682,10 +1682,10 @@
         <v>12</v>
       </c>
       <c r="AA5" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AB5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AC5" t="n">
         <v>10.5</v>
@@ -1694,127 +1694,127 @@
         <v>11</v>
       </c>
       <c r="AE5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AF5" t="n">
         <v>55</v>
       </c>
       <c r="AG5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ5" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AK5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL5" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
       </c>
       <c r="AN5" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AO5" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP5" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AR5" t="n">
         <v>4.5</v>
       </c>
       <c r="AS5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>5.2</v>
       </c>
-      <c r="AT5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX5" t="n">
+      <c r="BA5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC5" t="n">
         <v>6.4</v>
       </c>
-      <c r="AY5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC5" t="n">
+      <c r="BD5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE5" t="n">
         <v>6.6</v>
       </c>
-      <c r="BD5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BF5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH5" t="n">
         <v>4.1</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK5" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO5" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT5" t="n">
         <v>4.7</v>
@@ -1823,26 +1823,26 @@
         <v>3.5</v>
       </c>
       <c r="BV5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BX5" t="n">
         <v>25</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ5" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 14:36:03</t>
+          <t>2026-06-03 16:43:36</t>
         </is>
       </c>
     </row>
@@ -1873,82 +1873,82 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="G6" t="n">
         <v>3.05</v>
       </c>
       <c r="H6" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="J6" t="n">
-        <v>2.74</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>3.45</v>
+        <v>5.6</v>
       </c>
       <c r="O6" t="n">
         <v>1.17</v>
       </c>
       <c r="P6" t="n">
-        <v>2.26</v>
+        <v>2.54</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R6" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="S6" t="n">
         <v>2.26</v>
       </c>
       <c r="T6" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="U6" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="V6" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="W6" t="n">
         <v>1.49</v>
       </c>
       <c r="X6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y6" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA6" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AB6" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AC6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE6" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AF6" t="n">
         <v>25</v>
@@ -1957,10 +1957,10 @@
         <v>15.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AJ6" t="n">
         <v>44</v>
@@ -1972,131 +1972,131 @@
         <v>36</v>
       </c>
       <c r="AM6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN6" t="n">
         <v>16.5</v>
       </c>
       <c r="AO6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX6" t="n">
         <v>19</v>
       </c>
-      <c r="AP6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AS6" t="n">
+      <c r="AY6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG6" t="n">
         <v>3.9</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="BH6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI6" t="n">
         <v>3.5</v>
       </c>
-      <c r="AU6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.82</v>
-      </c>
       <c r="BJ6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BN6" t="n">
         <v>6.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.35</v>
+        <v>5.4</v>
       </c>
       <c r="BP6" t="n">
         <v>19</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BR6" t="n">
         <v>27</v>
       </c>
       <c r="BS6" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BT6" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="BV6" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BX6" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BY6" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BZ6" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 14:36:03</t>
+          <t>2026-06-03 16:43:36</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="I7" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L7" t="n">
         <v>1.43</v>
@@ -2151,7 +2151,7 @@
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="O7" t="n">
         <v>1.46</v>
@@ -2160,7 +2160,7 @@
         <v>1.61</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="R7" t="n">
         <v>1.23</v>
@@ -2175,10 +2175,10 @@
         <v>1.89</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -2235,16 +2235,16 @@
         <v>48</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AT7" t="n">
         <v>3.35</v>
@@ -2256,40 +2256,40 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="BE7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BG7" t="n">
         <v>4.4</v>
       </c>
-      <c r="BF7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BH7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI7" t="n">
         <v>2.4</v>
@@ -2316,7 +2316,7 @@
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-03 14:36:03</t>
+          <t>2026-06-03 16:43:36</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.27</v>
       </c>
       <c r="G8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="H8" t="n">
         <v>14</v>
@@ -2537,7 +2537,7 @@
         <v>1.83</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="BG8" t="n">
         <v>1.84</v>
@@ -2564,7 +2564,7 @@
         <v>3.55</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
@@ -2582,7 +2582,7 @@
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-03 14:36:03</t>
+          <t>2026-06-03 16:43:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -857,172 +857,172 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="G2" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="H2" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="I2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>1.02</v>
+        <v>5.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="R2" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="T2" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="U2" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="V2" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="X2" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="Y2" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="Z2" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="AA2" t="n">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
         <v>970</v>
       </c>
       <c r="AC2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD2" t="n">
         <v>970</v>
       </c>
-      <c r="AD2" t="n">
-        <v>21</v>
-      </c>
       <c r="AE2" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="AF2" t="n">
         <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH2" t="n">
         <v>970</v>
       </c>
       <c r="AI2" t="n">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="AJ2" t="n">
-        <v>26</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
         <v>970</v>
       </c>
       <c r="AL2" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="AM2" t="n">
-        <v>60</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>7.8</v>
+        <v>55</v>
       </c>
       <c r="AO2" t="n">
-        <v>27</v>
+        <v>260</v>
       </c>
       <c r="AP2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH2" t="n">
         <v>4.8</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BI2" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
@@ -1034,53 +1034,53 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>2.24</v>
+        <v>1.54</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.26</v>
+        <v>1.55</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="G3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H3" t="n">
         <v>4.6</v>
@@ -1123,10 +1123,10 @@
         <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.47</v>
@@ -1135,19 +1135,19 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O3" t="n">
         <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q3" t="n">
         <v>2.18</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S3" t="n">
         <v>4.1</v>
@@ -1156,13 +1156,13 @@
         <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V3" t="n">
         <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X3" t="n">
         <v>12</v>
@@ -1183,7 +1183,7 @@
         <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
         <v>80</v>
@@ -1195,10 +1195,10 @@
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AI3" t="n">
-        <v>90</v>
+        <v>370</v>
       </c>
       <c r="AJ3" t="n">
         <v>23</v>
@@ -1207,10 +1207,10 @@
         <v>24</v>
       </c>
       <c r="AL3" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AM3" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
         <v>18</v>
@@ -1225,7 +1225,7 @@
         <v>12.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AS3" t="n">
         <v>9.800000000000001</v>
@@ -1240,7 +1240,7 @@
         <v>17</v>
       </c>
       <c r="AW3" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AX3" t="n">
         <v>9.4</v>
@@ -1252,7 +1252,7 @@
         <v>19.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.4</v>
+        <v>28</v>
       </c>
       <c r="BB3" t="n">
         <v>19</v>
@@ -1264,19 +1264,19 @@
         <v>38</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF3" t="n">
         <v>14.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BH3" t="n">
         <v>3.15</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.74</v>
+        <v>2.54</v>
       </c>
       <c r="BJ3" t="n">
         <v>11.5</v>
@@ -1312,7 +1312,7 @@
         <v>8.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>3.25</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
         <v>4.8</v>
@@ -1389,7 +1389,7 @@
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>1.02</v>
+        <v>6.6</v>
       </c>
       <c r="O4" t="n">
         <v>1.14</v>
@@ -1404,13 +1404,13 @@
         <v>1.77</v>
       </c>
       <c r="S4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T4" t="n">
         <v>1.44</v>
       </c>
       <c r="U4" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="V4" t="n">
         <v>1.44</v>
@@ -1419,112 +1419,112 @@
         <v>1.71</v>
       </c>
       <c r="X4" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="Y4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="Z4" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AA4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AB4" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AF4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AG4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH4" t="n">
         <v>15</v>
       </c>
-      <c r="AH4" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AI4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ4" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AM4" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AN4" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AO4" t="n">
         <v>18</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.85</v>
+        <v>16</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.65</v>
+        <v>18.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.75</v>
+        <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.6</v>
+        <v>15.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.25</v>
+        <v>9.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.45</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.75</v>
+        <v>14.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.6</v>
+        <v>17</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.3</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.4</v>
+        <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.8</v>
+        <v>16</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.8</v>
+        <v>13</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.6</v>
+        <v>17</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.7</v>
+        <v>20</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.05</v>
+        <v>7.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.45</v>
+        <v>12</v>
       </c>
       <c r="BH4" t="n">
         <v>5.3</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>
@@ -1628,10 +1628,10 @@
         <v>1.66</v>
       </c>
       <c r="I5" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K5" t="n">
         <v>4.9</v>
@@ -1643,97 +1643,97 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P5" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="R5" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="S5" t="n">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="T5" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="U5" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V5" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="W5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X5" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="Y5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC5" t="n">
         <v>11</v>
       </c>
-      <c r="Z5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA5" t="n">
+      <c r="AD5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AH5" t="n">
         <v>19</v>
       </c>
-      <c r="AB5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AI5" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
+        <v>150</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN5" t="n">
         <v>65</v>
       </c>
-      <c r="AL5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>75</v>
-      </c>
       <c r="AO5" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AP5" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="AS5" t="n">
         <v>14.5</v>
@@ -1742,40 +1742,40 @@
         <v>14.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AY5" t="n">
         <v>14</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG5" t="n">
         <v>7.4</v>
@@ -1784,7 +1784,7 @@
         <v>4.1</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="BJ5" t="n">
         <v>10</v>
@@ -1796,19 +1796,19 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1826,7 +1826,7 @@
         <v>12</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BX5" t="n">
         <v>25</v>
@@ -1835,14 +1835,14 @@
         <v>7</v>
       </c>
       <c r="BZ5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA5" t="n">
         <v>6.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
         <v>2.38</v>
       </c>
       <c r="I6" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="J6" t="n">
         <v>3.55</v>
@@ -1894,7 +1894,7 @@
         <v>1.23</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N6" t="n">
         <v>5.6</v>
@@ -1921,13 +1921,13 @@
         <v>2.66</v>
       </c>
       <c r="V6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W6" t="n">
         <v>1.49</v>
       </c>
       <c r="X6" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Y6" t="n">
         <v>17.5</v>
@@ -1936,16 +1936,16 @@
         <v>25</v>
       </c>
       <c r="AA6" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AB6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AC6" t="n">
         <v>11.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE6" t="n">
         <v>28</v>
@@ -1954,28 +1954,28 @@
         <v>25</v>
       </c>
       <c r="AG6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AJ6" t="n">
         <v>44</v>
       </c>
       <c r="AK6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM6" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="AN6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO6" t="n">
         <v>15.5</v>
@@ -1987,22 +1987,22 @@
         <v>12</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.3</v>
+        <v>17.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AT6" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.4</v>
+        <v>19.5</v>
       </c>
       <c r="AX6" t="n">
         <v>19</v>
@@ -2011,34 +2011,34 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BF6" t="n">
         <v>11</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.9</v>
+        <v>11</v>
       </c>
       <c r="BH6" t="n">
         <v>4.7</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="BJ6" t="n">
         <v>8.800000000000001</v>
@@ -2056,7 +2056,7 @@
         <v>6.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BP6" t="n">
         <v>19</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G7" t="n">
         <v>3.4</v>
@@ -2136,31 +2136,31 @@
         <v>2.64</v>
       </c>
       <c r="I7" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K7" t="n">
         <v>3.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="O7" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R7" t="n">
         <v>1.23</v>
@@ -2172,82 +2172,82 @@
         <v>1.92</v>
       </c>
       <c r="U7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V7" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="Z7" t="n">
         <v>970</v>
       </c>
       <c r="AA7" t="n">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
         <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AD7" t="n">
         <v>970</v>
       </c>
       <c r="AE7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF7" t="n">
         <v>44</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>24</v>
       </c>
       <c r="AG7" t="n">
         <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="AI7" t="n">
-        <v>70</v>
+        <v>290</v>
       </c>
       <c r="AJ7" t="n">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="AL7" t="n">
+        <v>300</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO7" t="n">
         <v>75</v>
       </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>48</v>
-      </c>
       <c r="AP7" t="n">
-        <v>3.45</v>
+        <v>7.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="AR7" t="n">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.35</v>
+        <v>5.6</v>
       </c>
       <c r="AU7" t="n">
         <v>5.3</v>
@@ -2256,55 +2256,55 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="AX7" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.85</v>
+        <v>7.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.15</v>
+        <v>4.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH7" t="n">
         <v>4.7</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
@@ -2316,13 +2316,13 @@
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
@@ -2334,23 +2334,23 @@
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>
@@ -2384,22 +2384,22 @@
         <v>1.27</v>
       </c>
       <c r="G8" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="H8" t="n">
         <v>14</v>
       </c>
       <c r="I8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J8" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="K8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
@@ -2414,7 +2414,7 @@
         <v>1.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R8" t="n">
         <v>1.36</v>
@@ -2423,22 +2423,22 @@
         <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="U8" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="V8" t="n">
         <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="X8" t="n">
         <v>970</v>
       </c>
       <c r="Y8" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -2447,13 +2447,13 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AD8" t="n">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
@@ -2462,91 +2462,91 @@
         <v>970</v>
       </c>
       <c r="AG8" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AH8" t="n">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>970</v>
+        <v>180</v>
       </c>
       <c r="AK8" t="n">
         <v>970</v>
       </c>
       <c r="AL8" t="n">
-        <v>70</v>
+        <v>330</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.46</v>
+        <v>4.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.84</v>
+        <v>4.2</v>
       </c>
       <c r="AT8" t="n">
         <v>5.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.15</v>
+        <v>7.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.83</v>
+        <v>4.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.3</v>
+        <v>3.85</v>
       </c>
       <c r="AY8" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.83</v>
+        <v>4.2</v>
       </c>
       <c r="BB8" t="n">
         <v>7.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.15</v>
+        <v>7.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.84</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
@@ -2558,53 +2558,53 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="BN8" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>2.12</v>
+        <v>3.8</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>13</v>
+        <v>6.6</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>2.1</v>
+        <v>3.45</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-03 16:43:36</t>
+          <t>2026-06-03 18:51:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="G2" t="n">
         <v>2.04</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I2" t="n">
         <v>4.6</v>
@@ -884,25 +884,25 @@
         <v>5.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="Q2" t="n">
         <v>1.57</v>
       </c>
       <c r="R2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S2" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="T2" t="n">
         <v>1.56</v>
       </c>
       <c r="U2" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V2" t="n">
         <v>1.27</v>
@@ -911,10 +911,10 @@
         <v>1.96</v>
       </c>
       <c r="X2" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="Y2" t="n">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="Z2" t="n">
         <v>80</v>
@@ -938,7 +938,7 @@
         <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AH2" t="n">
         <v>970</v>
@@ -965,64 +965,64 @@
         <v>260</v>
       </c>
       <c r="AP2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>6</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AR2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AV2" t="n">
         <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BD2" t="n">
         <v>17.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH2" t="n">
         <v>4.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
@@ -1037,7 +1037,7 @@
         <v>1.59</v>
       </c>
       <c r="BN2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BO2" t="n">
         <v>3.3</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 18:51:00</t>
+          <t>2026-06-03 20:58:44</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="G3" t="n">
         <v>1.98</v>
@@ -1123,31 +1123,31 @@
         <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="R3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S3" t="n">
         <v>4.1</v>
@@ -1156,19 +1156,19 @@
         <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V3" t="n">
         <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z3" t="n">
         <v>36</v>
@@ -1180,7 +1180,7 @@
         <v>7.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD3" t="n">
         <v>20</v>
@@ -1189,7 +1189,7 @@
         <v>80</v>
       </c>
       <c r="AF3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
@@ -1201,10 +1201,10 @@
         <v>370</v>
       </c>
       <c r="AJ3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK3" t="n">
         <v>23</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>24</v>
       </c>
       <c r="AL3" t="n">
         <v>110</v>
@@ -1213,7 +1213,7 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO3" t="n">
         <v>110</v>
@@ -1222,19 +1222,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
         <v>16</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
         <v>17</v>
@@ -1243,13 +1243,13 @@
         <v>55</v>
       </c>
       <c r="AX3" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AY3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
         <v>28</v>
@@ -1258,37 +1258,37 @@
         <v>19</v>
       </c>
       <c r="BC3" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD3" t="n">
         <v>38</v>
       </c>
       <c r="BE3" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="BJ3" t="n">
         <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN3" t="n">
         <v>4.5</v>
@@ -1300,41 +1300,41 @@
         <v>14.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
         <v>8.6</v>
       </c>
-      <c r="BT3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 18:51:00</t>
+          <t>2026-06-03 20:58:44</t>
         </is>
       </c>
     </row>
@@ -1365,58 +1365,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="I4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
         <v>4.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.14</v>
       </c>
       <c r="P4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U4" t="n">
         <v>2.88</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="V4" t="n">
         <v>1.43</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.44</v>
-      </c>
       <c r="W4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X4" t="n">
         <v>36</v>
@@ -1431,13 +1431,13 @@
         <v>50</v>
       </c>
       <c r="AB4" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AC4" t="n">
         <v>12</v>
       </c>
       <c r="AD4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
         <v>29</v>
@@ -1452,103 +1452,103 @@
         <v>15</v>
       </c>
       <c r="AI4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AJ4" t="n">
         <v>32</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM4" t="n">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX4" t="n">
         <v>18</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>17</v>
       </c>
       <c r="AY4" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BB4" t="n">
         <v>13</v>
       </c>
       <c r="BC4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE4" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BH4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="BJ4" t="n">
         <v>8.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BL4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BN4" t="n">
         <v>6.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="BP4" t="n">
         <v>15</v>
@@ -1563,10 +1563,10 @@
         <v>6.6</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV4" t="n">
         <v>21</v>
@@ -1575,20 +1575,20 @@
         <v>6.6</v>
       </c>
       <c r="BX4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BY4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 18:51:00</t>
+          <t>2026-06-03 20:58:44</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G5" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="H5" t="n">
         <v>1.66</v>
@@ -1634,25 +1634,25 @@
         <v>4.1</v>
       </c>
       <c r="K5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
         <v>1.22</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="R5" t="n">
         <v>1.51</v>
@@ -1661,16 +1661,16 @@
         <v>2.56</v>
       </c>
       <c r="T5" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U5" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="V5" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="W5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X5" t="n">
         <v>38</v>
@@ -1697,13 +1697,13 @@
         <v>16.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AG5" t="n">
         <v>34</v>
       </c>
       <c r="AH5" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
         <v>75</v>
@@ -1712,16 +1712,16 @@
         <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AL5" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>65</v>
+        <v>700</v>
       </c>
       <c r="AO5" t="n">
         <v>9</v>
@@ -1730,7 +1730,7 @@
         <v>16.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR5" t="n">
         <v>10</v>
@@ -1745,37 +1745,37 @@
         <v>8.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AW5" t="n">
         <v>13</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY5" t="n">
         <v>14</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.9</v>
+        <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BG5" t="n">
         <v>7.4</v>
@@ -1784,7 +1784,7 @@
         <v>4.1</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ5" t="n">
         <v>10</v>
@@ -1802,7 +1802,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BO5" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 18:51:00</t>
+          <t>2026-06-03 20:58:44</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         <v>3.05</v>
       </c>
       <c r="H6" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I6" t="n">
         <v>2.76</v>
@@ -1900,7 +1900,7 @@
         <v>5.6</v>
       </c>
       <c r="O6" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P6" t="n">
         <v>2.54</v>
@@ -1927,7 +1927,7 @@
         <v>1.49</v>
       </c>
       <c r="X6" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="Y6" t="n">
         <v>17.5</v>
@@ -1957,7 +1957,7 @@
         <v>14.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI6" t="n">
         <v>65</v>
@@ -1990,7 +1990,7 @@
         <v>17.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT6" t="n">
         <v>16.5</v>
@@ -2017,7 +2017,7 @@
         <v>14.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BC6" t="n">
         <v>11.5</v>
@@ -2038,7 +2038,7 @@
         <v>4.7</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="BJ6" t="n">
         <v>8.800000000000001</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 18:51:00</t>
+          <t>2026-06-03 20:58:44</t>
         </is>
       </c>
     </row>
@@ -2130,10 +2130,10 @@
         <v>2.96</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H7" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I7" t="n">
         <v>2.94</v>
@@ -2169,22 +2169,22 @@
         <v>4</v>
       </c>
       <c r="T7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.92</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.9</v>
       </c>
       <c r="V7" t="n">
         <v>1.52</v>
       </c>
       <c r="W7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
         <v>970</v>
@@ -2199,7 +2199,7 @@
         <v>11.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AE7" t="n">
         <v>110</v>
@@ -2211,7 +2211,7 @@
         <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>46</v>
+        <v>950</v>
       </c>
       <c r="AI7" t="n">
         <v>290</v>
@@ -2244,7 +2244,7 @@
         <v>8.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT7" t="n">
         <v>5.6</v>
@@ -2253,43 +2253,43 @@
         <v>5.3</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
-        <v>16</v>
+        <v>4.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="AY7" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="BA7" t="n">
         <v>4.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="BC7" t="n">
         <v>4.7</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="BE7" t="n">
         <v>3.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BG7" t="n">
         <v>7.2</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BI7" t="n">
         <v>2.42</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-03 18:51:00</t>
+          <t>2026-06-03 20:58:44</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.27</v>
       </c>
       <c r="G8" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="H8" t="n">
         <v>14</v>
@@ -2393,10 +2393,10 @@
         <v>22</v>
       </c>
       <c r="J8" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="K8" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="L8" t="n">
         <v>1.35</v>
@@ -2411,10 +2411,10 @@
         <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="R8" t="n">
         <v>1.36</v>
@@ -2432,13 +2432,13 @@
         <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X8" t="n">
         <v>970</v>
       </c>
       <c r="Y8" t="n">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -2450,22 +2450,22 @@
         <v>12.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AD8" t="n">
-        <v>300</v>
+        <v>950</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG8" t="n">
         <v>970</v>
       </c>
-      <c r="AG8" t="n">
-        <v>24</v>
-      </c>
       <c r="AH8" t="n">
-        <v>160</v>
+        <v>950</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
@@ -2492,7 +2492,7 @@
         <v>7.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR8" t="n">
         <v>4.2</v>
@@ -2507,19 +2507,19 @@
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AW8" t="n">
         <v>4.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AY8" t="n">
         <v>7</v>
       </c>
       <c r="AZ8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA8" t="n">
         <v>4.2</v>
@@ -2531,16 +2531,16 @@
         <v>9</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH8" t="n">
         <v>3.85</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-03 18:51:00</t>
+          <t>2026-06-03 20:58:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="G2" t="n">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="H2" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.24</v>
@@ -881,34 +881,34 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="R2" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="S2" t="n">
         <v>2.32</v>
       </c>
       <c r="T2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="U2" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="X2" t="n">
         <v>950</v>
@@ -917,7 +917,7 @@
         <v>950</v>
       </c>
       <c r="Z2" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AA2" t="n">
         <v>900</v>
@@ -926,25 +926,25 @@
         <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>42</v>
+        <v>17.5</v>
       </c>
       <c r="AD2" t="n">
         <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AG2" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="AH2" t="n">
         <v>970</v>
       </c>
       <c r="AI2" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AJ2" t="n">
         <v>900</v>
@@ -953,7 +953,7 @@
         <v>970</v>
       </c>
       <c r="AL2" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
@@ -962,25 +962,25 @@
         <v>55</v>
       </c>
       <c r="AO2" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AP2" t="n">
         <v>6.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR2" t="n">
         <v>6.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="AT2" t="n">
         <v>5.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AV2" t="n">
         <v>13</v>
@@ -992,22 +992,22 @@
         <v>5.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AZ2" t="n">
         <v>5.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="BB2" t="n">
         <v>6</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>17.5</v>
+        <v>6.2</v>
       </c>
       <c r="BE2" t="n">
         <v>7.2</v>
@@ -1016,13 +1016,13 @@
         <v>4.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH2" t="n">
         <v>4.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
@@ -1034,25 +1034,25 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.59</v>
+        <v>1.92</v>
       </c>
       <c r="BN2" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
@@ -1064,23 +1064,23 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.54</v>
+        <v>1.84</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.55</v>
+        <v>2.82</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 20:58:44</t>
+          <t>2026-06-03 23:05:53</t>
         </is>
       </c>
     </row>
@@ -1111,25 +1111,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="G3" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="H3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I3" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="J3" t="n">
         <v>3.55</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
@@ -1159,7 +1159,7 @@
         <v>1.86</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W3" t="n">
         <v>2.04</v>
@@ -1171,10 +1171,10 @@
         <v>15.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA3" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB3" t="n">
         <v>7.8</v>
@@ -1186,7 +1186,7 @@
         <v>20</v>
       </c>
       <c r="AE3" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AF3" t="n">
         <v>11</v>
@@ -1195,10 +1195,10 @@
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AI3" t="n">
-        <v>370</v>
+        <v>700</v>
       </c>
       <c r="AJ3" t="n">
         <v>22</v>
@@ -1210,37 +1210,37 @@
         <v>110</v>
       </c>
       <c r="AM3" t="n">
-        <v>580</v>
+        <v>170</v>
       </c>
       <c r="AN3" t="n">
         <v>17</v>
       </c>
       <c r="AO3" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR3" t="n">
         <v>16</v>
       </c>
       <c r="AS3" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU3" t="n">
         <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="AX3" t="n">
         <v>9</v>
@@ -1249,19 +1249,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="BB3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC3" t="n">
         <v>18.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="BE3" t="n">
         <v>12.5</v>
@@ -1276,7 +1276,7 @@
         <v>3.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BJ3" t="n">
         <v>11.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 20:58:44</t>
+          <t>2026-06-03 23:05:53</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>2.38</v>
       </c>
       <c r="H4" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I4" t="n">
         <v>3.3</v>
@@ -1476,7 +1476,7 @@
         <v>7.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR4" t="n">
         <v>19</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 20:58:44</t>
+          <t>2026-06-03 23:05:53</t>
         </is>
       </c>
     </row>
@@ -1622,16 +1622,16 @@
         <v>4.7</v>
       </c>
       <c r="G5" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="I5" t="n">
         <v>1.74</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K5" t="n">
         <v>4.8</v>
@@ -1643,19 +1643,19 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O5" t="n">
         <v>1.22</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q5" t="n">
         <v>1.61</v>
       </c>
       <c r="R5" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S5" t="n">
         <v>2.56</v>
@@ -1664,7 +1664,7 @@
         <v>1.61</v>
       </c>
       <c r="U5" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V5" t="n">
         <v>2.34</v>
@@ -1676,7 +1676,7 @@
         <v>38</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z5" t="n">
         <v>13</v>
@@ -1724,13 +1724,13 @@
         <v>700</v>
       </c>
       <c r="AO5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP5" t="n">
-        <v>16.5</v>
+        <v>6.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR5" t="n">
         <v>10</v>
@@ -1745,13 +1745,13 @@
         <v>8.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AW5" t="n">
         <v>13</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY5" t="n">
         <v>14</v>
@@ -1760,89 +1760,89 @@
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC5" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC5" t="n">
+      <c r="BD5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE5" t="n">
         <v>7.8</v>
       </c>
-      <c r="BD5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF5" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="BJ5" t="n">
         <v>10</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN5" t="n">
         <v>9</v>
       </c>
-      <c r="BN5" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BO5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BV5" t="n">
         <v>12</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BX5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BY5" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BZ5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 20:58:44</t>
+          <t>2026-06-03 23:05:53</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>2.76</v>
       </c>
       <c r="J6" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
         <v>4.2</v>
@@ -1912,7 +1912,7 @@
         <v>1.62</v>
       </c>
       <c r="S6" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T6" t="n">
         <v>1.49</v>
@@ -1978,7 +1978,7 @@
         <v>16</v>
       </c>
       <c r="AO6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AP6" t="n">
         <v>18</v>
@@ -1990,7 +1990,7 @@
         <v>17.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT6" t="n">
         <v>16.5</v>
@@ -2017,7 +2017,7 @@
         <v>14.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC6" t="n">
         <v>11.5</v>
@@ -2026,7 +2026,7 @@
         <v>14.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF6" t="n">
         <v>11</v>
@@ -2056,7 +2056,7 @@
         <v>6.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP6" t="n">
         <v>19</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 20:58:44</t>
+          <t>2026-06-03 23:05:53</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="H7" t="n">
         <v>2.62</v>
       </c>
       <c r="I7" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J7" t="n">
         <v>2.82</v>
@@ -2160,7 +2160,7 @@
         <v>1.62</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="R7" t="n">
         <v>1.23</v>
@@ -2172,19 +2172,19 @@
         <v>1.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V7" t="n">
         <v>1.52</v>
       </c>
       <c r="W7" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="Z7" t="n">
         <v>970</v>
@@ -2202,10 +2202,10 @@
         <v>26</v>
       </c>
       <c r="AE7" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AG7" t="n">
         <v>970</v>
@@ -2214,25 +2214,25 @@
         <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
         <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AL7" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AO7" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AP7" t="n">
         <v>7.4</v>
@@ -2244,7 +2244,7 @@
         <v>8.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AT7" t="n">
         <v>5.6</v>
@@ -2256,7 +2256,7 @@
         <v>7</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AX7" t="n">
         <v>9</v>
@@ -2274,10 +2274,10 @@
         <v>4.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BE7" t="n">
         <v>3.4</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-03 20:58:44</t>
+          <t>2026-06-03 23:05:53</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
         <v>1.31</v>
       </c>
       <c r="H8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="I8" t="n">
         <v>22</v>
@@ -2414,7 +2414,7 @@
         <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="R8" t="n">
         <v>1.36</v>
@@ -2426,7 +2426,7 @@
         <v>2.6</v>
       </c>
       <c r="U8" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
         <v>1.05</v>
@@ -2471,7 +2471,7 @@
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="AK8" t="n">
         <v>970</v>
@@ -2501,13 +2501,13 @@
         <v>4.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AW8" t="n">
         <v>4.2</v>
@@ -2531,13 +2531,13 @@
         <v>9</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BG8" t="n">
         <v>9.6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-03 20:58:44</t>
+          <t>2026-06-03 23:05:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -857,55 +857,55 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="G2" t="n">
         <v>1.82</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K2" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
         <v>5.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="S2" t="n">
         <v>2.32</v>
       </c>
       <c r="T2" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="U2" t="n">
         <v>2.44</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W2" t="n">
         <v>2.2</v>
@@ -920,7 +920,7 @@
         <v>500</v>
       </c>
       <c r="AA2" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB2" t="n">
         <v>970</v>
@@ -935,10 +935,10 @@
         <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>40</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
         <v>970</v>
@@ -947,10 +947,10 @@
         <v>500</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK2" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AL2" t="n">
         <v>500</v>
@@ -962,125 +962,125 @@
         <v>55</v>
       </c>
       <c r="AO2" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="AT2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU2" t="n">
         <v>5.1</v>
       </c>
-      <c r="AU2" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AV2" t="n">
-        <v>13</v>
+        <v>5.3</v>
       </c>
       <c r="AW2" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BB2" t="n">
         <v>6</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="BF2" t="n">
         <v>4.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="BH2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK2" t="n">
         <v>4.8</v>
       </c>
-      <c r="BI2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.92</v>
+        <v>3.1</v>
       </c>
       <c r="BN2" t="n">
-        <v>18</v>
+        <v>5.3</v>
       </c>
       <c r="BO2" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA2" t="n">
         <v>6</v>
       </c>
-      <c r="BT2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>5.4</v>
-      </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-03 23:05:53</t>
+          <t>2026-06-04 01:13:30</t>
         </is>
       </c>
     </row>
@@ -1111,40 +1111,40 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="G3" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="H3" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P3" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R3" t="n">
         <v>1.27</v>
@@ -1153,188 +1153,188 @@
         <v>4.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U3" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="V3" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="W3" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="X3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y3" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA3" t="n">
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE3" t="n">
         <v>170</v>
       </c>
       <c r="AF3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI3" t="n">
-        <v>700</v>
+        <v>190</v>
       </c>
       <c r="AJ3" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AK3" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="AL3" t="n">
         <v>110</v>
       </c>
       <c r="AM3" t="n">
-        <v>170</v>
+        <v>450</v>
       </c>
       <c r="AN3" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="AO3" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS3" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AT3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU3" t="n">
         <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AW3" t="n">
-        <v>28</v>
+        <v>11.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA3" t="n">
         <v>12</v>
       </c>
       <c r="BB3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BC3" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BD3" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="BE3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF3" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="BG3" t="n">
-        <v>12.5</v>
+        <v>42</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="BP3" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT3" t="n">
         <v>7.8</v>
       </c>
-      <c r="BT3" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BU3" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-03 23:05:53</t>
+          <t>2026-06-04 01:13:30</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G4" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="H4" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J4" t="n">
         <v>4.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
@@ -1395,28 +1395,28 @@
         <v>1.14</v>
       </c>
       <c r="P4" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R4" t="n">
         <v>1.8</v>
       </c>
       <c r="S4" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="U4" t="n">
         <v>2.88</v>
       </c>
       <c r="V4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W4" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="X4" t="n">
         <v>36</v>
@@ -1425,25 +1425,25 @@
         <v>23</v>
       </c>
       <c r="Z4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AC4" t="n">
         <v>12</v>
       </c>
       <c r="AD4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
         <v>29</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
         <v>13</v>
@@ -1452,10 +1452,10 @@
         <v>15</v>
       </c>
       <c r="AI4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AJ4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK4" t="n">
         <v>21</v>
@@ -1467,82 +1467,82 @@
         <v>95</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO4" t="n">
         <v>17.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ4" t="n">
         <v>19.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS4" t="n">
         <v>7.8</v>
       </c>
       <c r="AT4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX4" t="n">
         <v>16.5</v>
       </c>
-      <c r="AU4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>18</v>
-      </c>
       <c r="AY4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>10.5</v>
+        <v>5.7</v>
       </c>
       <c r="BA4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB4" t="n">
         <v>13</v>
       </c>
       <c r="BC4" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE4" t="n">
         <v>7.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BH4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BJ4" t="n">
         <v>8.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN4" t="n">
         <v>6.2</v>
@@ -1554,13 +1554,13 @@
         <v>15</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BR4" t="n">
         <v>21</v>
       </c>
       <c r="BS4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT4" t="n">
         <v>7.4</v>
@@ -1572,23 +1572,23 @@
         <v>21</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BY4" t="n">
         <v>6.8</v>
       </c>
       <c r="BZ4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-03 23:05:53</t>
+          <t>2026-06-04 01:13:30</t>
         </is>
       </c>
     </row>
@@ -1622,22 +1622,22 @@
         <v>4.7</v>
       </c>
       <c r="G5" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="H5" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="I5" t="n">
         <v>1.74</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K5" t="n">
         <v>4.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
@@ -1646,31 +1646,31 @@
         <v>4.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P5" t="n">
         <v>2.36</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="R5" t="n">
         <v>1.52</v>
       </c>
       <c r="S5" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="T5" t="n">
         <v>1.61</v>
       </c>
       <c r="U5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V5" t="n">
         <v>2.34</v>
       </c>
       <c r="W5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X5" t="n">
         <v>38</v>
@@ -1727,22 +1727,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.6</v>
+        <v>17</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="AR5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AT5" t="n">
-        <v>14.5</v>
+        <v>6.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV5" t="n">
         <v>4.6</v>
@@ -1751,10 +1751,10 @@
         <v>13</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="AY5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>14.5</v>
@@ -1790,13 +1790,13 @@
         <v>10</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN5" t="n">
         <v>9</v>
@@ -1826,23 +1826,23 @@
         <v>12</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BX5" t="n">
         <v>24</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BZ5" t="n">
         <v>17.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-03 23:05:53</t>
+          <t>2026-06-04 01:13:30</t>
         </is>
       </c>
     </row>
@@ -1873,25 +1873,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G6" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I6" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K6" t="n">
         <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="M6" t="n">
         <v>1.03</v>
@@ -1900,31 +1900,31 @@
         <v>5.6</v>
       </c>
       <c r="O6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P6" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="R6" t="n">
         <v>1.62</v>
       </c>
       <c r="S6" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="T6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U6" t="n">
         <v>2.66</v>
       </c>
       <c r="V6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W6" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="X6" t="n">
         <v>50</v>
@@ -1933,7 +1933,7 @@
         <v>17.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA6" t="n">
         <v>85</v>
@@ -1975,10 +1975,10 @@
         <v>200</v>
       </c>
       <c r="AN6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AP6" t="n">
         <v>18</v>
@@ -1990,7 +1990,7 @@
         <v>17.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT6" t="n">
         <v>16.5</v>
@@ -2017,7 +2017,7 @@
         <v>14.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC6" t="n">
         <v>11.5</v>
@@ -2056,7 +2056,7 @@
         <v>6.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP6" t="n">
         <v>19</v>
@@ -2065,7 +2065,7 @@
         <v>6.2</v>
       </c>
       <c r="BR6" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
         <v>7</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-03 23:05:53</t>
+          <t>2026-06-04 01:13:30</t>
         </is>
       </c>
     </row>
@@ -2127,58 +2127,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="H7" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I7" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="J7" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="K7" t="n">
         <v>3.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P7" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="R7" t="n">
         <v>1.23</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="U7" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V7" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W7" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -2196,10 +2196,10 @@
         <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AD7" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
         <v>500</v>
@@ -2211,7 +2211,7 @@
         <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI7" t="n">
         <v>500</v>
@@ -2235,19 +2235,19 @@
         <v>500</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AR7" t="n">
         <v>8.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU7" t="n">
         <v>5.3</v>
@@ -2256,7 +2256,7 @@
         <v>7</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="AX7" t="n">
         <v>9</v>
@@ -2268,61 +2268,61 @@
         <v>10.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.6</v>
+        <v>2.74</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.6</v>
+        <v>2.76</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.4</v>
+        <v>2.46</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="BG7" t="n">
         <v>7.2</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.9</v>
+        <v>2.92</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.1</v>
+        <v>1.54</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.07</v>
+        <v>1.47</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.1</v>
+        <v>1.43</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
@@ -2334,23 +2334,23 @@
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.08</v>
+        <v>1.41</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.08</v>
+        <v>1.41</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-03 23:05:53</t>
+          <t>2026-06-04 01:13:30</t>
         </is>
       </c>
     </row>
@@ -2381,52 +2381,52 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="G8" t="n">
         <v>1.31</v>
       </c>
       <c r="H8" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="I8" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="J8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K8" t="n">
         <v>6.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="O8" t="n">
         <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T8" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="V8" t="n">
         <v>1.05</v>
@@ -2471,7 +2471,7 @@
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="AK8" t="n">
         <v>970</v>
@@ -2492,7 +2492,7 @@
         <v>7.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR8" t="n">
         <v>4.2</v>
@@ -2501,110 +2501,110 @@
         <v>4.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="AW8" t="n">
         <v>4.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AY8" t="n">
         <v>7</v>
       </c>
       <c r="AZ8" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BA8" t="n">
         <v>4.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="BC8" t="n">
         <v>9</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BE8" t="n">
         <v>2.92</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BI8" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.75</v>
+        <v>3.95</v>
       </c>
       <c r="BN8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>6.6</v>
+        <v>3.95</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>6</v>
+        <v>3.05</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-03 23:05:53</t>
+          <t>2026-06-04 01:13:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -857,55 +857,55 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="G2" t="n">
         <v>1.82</v>
       </c>
       <c r="H2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
         <v>4.1</v>
       </c>
-      <c r="I2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4.2</v>
-      </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="R2" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="S2" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="T2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U2" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W2" t="n">
         <v>2.2</v>
@@ -923,13 +923,13 @@
         <v>500</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AC2" t="n">
         <v>17.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE2" t="n">
         <v>500</v>
@@ -938,10 +938,10 @@
         <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI2" t="n">
         <v>500</v>
@@ -950,7 +950,7 @@
         <v>500</v>
       </c>
       <c r="AK2" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AL2" t="n">
         <v>500</v>
@@ -959,46 +959,46 @@
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="AO2" t="n">
         <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AU2" t="n">
         <v>5.1</v>
       </c>
       <c r="AV2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>5.3</v>
       </c>
-      <c r="AW2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BA2" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="BB2" t="n">
         <v>6</v>
@@ -1010,77 +1010,77 @@
         <v>6.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BI2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO2" t="n">
         <v>3.25</v>
       </c>
-      <c r="BJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>2.32</v>
+        <v>6.4</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -1111,82 +1111,82 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="G3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2.12</v>
       </c>
-      <c r="H3" t="n">
+      <c r="R3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S3" t="n">
         <v>4</v>
       </c>
-      <c r="I3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4.1</v>
-      </c>
       <c r="T3" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="U3" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="X3" t="n">
         <v>12</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Z3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA3" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AB3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
-        <v>170</v>
+        <v>470</v>
       </c>
       <c r="AF3" t="n">
         <v>12</v>
@@ -1195,146 +1195,146 @@
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI3" t="n">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="AJ3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AK3" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AL3" t="n">
         <v>110</v>
       </c>
       <c r="AM3" t="n">
-        <v>450</v>
+        <v>160</v>
       </c>
       <c r="AN3" t="n">
-        <v>32</v>
+        <v>19.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="AR3" t="n">
-        <v>26</v>
+        <v>17.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="AT3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU3" t="n">
         <v>7.2</v>
       </c>
-      <c r="AU3" t="n">
-        <v>7</v>
-      </c>
       <c r="AV3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW3" t="n">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="AX3" t="n">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="BD3" t="n">
         <v>38</v>
       </c>
       <c r="BE3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BF3" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="BG3" t="n">
-        <v>42</v>
+        <v>8.6</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>10</v>
+        <v>2.26</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU3" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>10</v>
+        <v>2.26</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G4" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H4" t="n">
         <v>2.96</v>
       </c>
       <c r="I4" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.23</v>
@@ -1389,49 +1389,49 @@
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P4" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="S4" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="T4" t="n">
         <v>1.45</v>
       </c>
       <c r="U4" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="V4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W4" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X4" t="n">
         <v>36</v>
       </c>
       <c r="Y4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA4" t="n">
         <v>55</v>
       </c>
       <c r="AB4" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC4" t="n">
         <v>12</v>
@@ -1440,7 +1440,7 @@
         <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF4" t="n">
         <v>21</v>
@@ -1449,7 +1449,7 @@
         <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI4" t="n">
         <v>32</v>
@@ -1464,73 +1464,73 @@
         <v>25</v>
       </c>
       <c r="AM4" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="AN4" t="n">
         <v>9</v>
       </c>
       <c r="AO4" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19.5</v>
+        <v>6.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>15.5</v>
+        <v>6</v>
       </c>
       <c r="AU4" t="n">
-        <v>9.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>16.5</v>
+        <v>6.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="AZ4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG4" t="n">
         <v>5.7</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>13</v>
       </c>
       <c r="BH4" t="n">
         <v>5.3</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="BJ4" t="n">
         <v>8.6</v>
@@ -1539,7 +1539,7 @@
         <v>4.5</v>
       </c>
       <c r="BL4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
         <v>8.199999999999999</v>
@@ -1548,10 +1548,10 @@
         <v>6.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="BP4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ4" t="n">
         <v>5.8</v>
@@ -1560,19 +1560,19 @@
         <v>21</v>
       </c>
       <c r="BS4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT4" t="n">
         <v>7.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="BV4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX4" t="n">
         <v>25</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="I5" t="n">
         <v>1.74</v>
@@ -1643,28 +1643,28 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O5" t="n">
         <v>1.23</v>
       </c>
       <c r="P5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U5" t="n">
         <v>2.36</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.32</v>
       </c>
       <c r="V5" t="n">
         <v>2.34</v>
@@ -1679,10 +1679,10 @@
         <v>12.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AB5" t="n">
         <v>40</v>
@@ -1724,13 +1724,13 @@
         <v>700</v>
       </c>
       <c r="AO5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AP5" t="n">
         <v>17</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AR5" t="n">
         <v>10.5</v>
@@ -1739,70 +1739,70 @@
         <v>16</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.2</v>
+        <v>19.5</v>
       </c>
       <c r="AU5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="AW5" t="n">
         <v>13</v>
       </c>
       <c r="AX5" t="n">
-        <v>25</v>
+        <v>7.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG5" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>7</v>
-      </c>
       <c r="BH5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="BJ5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BN5" t="n">
         <v>9</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
@@ -1820,13 +1820,13 @@
         <v>4.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BV5" t="n">
         <v>12</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BX5" t="n">
         <v>24</v>
@@ -1835,14 +1835,14 @@
         <v>6.8</v>
       </c>
       <c r="BZ5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="CA5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -1873,25 +1873,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G6" t="n">
         <v>2.98</v>
       </c>
       <c r="H6" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="I6" t="n">
         <v>2.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M6" t="n">
         <v>1.03</v>
@@ -1900,7 +1900,7 @@
         <v>5.6</v>
       </c>
       <c r="O6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P6" t="n">
         <v>2.56</v>
@@ -1912,19 +1912,19 @@
         <v>1.62</v>
       </c>
       <c r="S6" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T6" t="n">
         <v>1.5</v>
       </c>
       <c r="U6" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="V6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W6" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X6" t="n">
         <v>50</v>
@@ -1948,7 +1948,7 @@
         <v>13.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AF6" t="n">
         <v>25</v>
@@ -1981,22 +1981,22 @@
         <v>14</v>
       </c>
       <c r="AP6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AR6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT6" t="n">
         <v>16.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV6" t="n">
         <v>10.5</v>
@@ -2005,10 +2005,10 @@
         <v>19.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ6" t="n">
         <v>11</v>
@@ -2017,7 +2017,7 @@
         <v>14.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC6" t="n">
         <v>11.5</v>
@@ -2026,10 +2026,10 @@
         <v>14.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BG6" t="n">
         <v>11</v>
@@ -2038,7 +2038,7 @@
         <v>4.7</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ6" t="n">
         <v>8.800000000000001</v>
@@ -2050,7 +2050,7 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN6" t="n">
         <v>6.6</v>
@@ -2059,13 +2059,13 @@
         <v>4.8</v>
       </c>
       <c r="BP6" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ6" t="n">
         <v>6.2</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS6" t="n">
         <v>7</v>
@@ -2074,13 +2074,13 @@
         <v>6.4</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV6" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BX6" t="n">
         <v>25</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -2127,64 +2127,64 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H7" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="I7" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="J7" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="O7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P7" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="R7" t="n">
         <v>1.23</v>
       </c>
       <c r="S7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T7" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V7" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="W7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X7" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y7" t="n">
         <v>970</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>950</v>
       </c>
       <c r="Z7" t="n">
         <v>970</v>
@@ -2196,10 +2196,10 @@
         <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AE7" t="n">
         <v>500</v>
@@ -2217,7 +2217,7 @@
         <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK7" t="n">
         <v>500</v>
@@ -2226,40 +2226,40 @@
         <v>500</v>
       </c>
       <c r="AM7" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO7" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP7" t="n">
         <v>5.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AR7" t="n">
         <v>8.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="AT7" t="n">
         <v>7.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="AV7" t="n">
         <v>7</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.35</v>
+        <v>26</v>
       </c>
       <c r="AX7" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AY7" t="n">
         <v>7.6</v>
@@ -2268,43 +2268,43 @@
         <v>10.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.74</v>
+        <v>2.42</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.76</v>
+        <v>2.42</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.46</v>
+        <v>2.86</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.2</v>
+        <v>27</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.54</v>
+        <v>1.16</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
@@ -2316,13 +2316,13 @@
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
@@ -2334,23 +2334,23 @@
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.41</v>
+        <v>1.13</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.41</v>
+        <v>1.13</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>
@@ -2387,10 +2387,10 @@
         <v>1.31</v>
       </c>
       <c r="H8" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="I8" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="J8" t="n">
         <v>5.6</v>
@@ -2405,28 +2405,28 @@
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
         <v>3.35</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="U8" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="V8" t="n">
         <v>1.05</v>
@@ -2435,22 +2435,22 @@
         <v>4.2</v>
       </c>
       <c r="X8" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="Y8" t="n">
         <v>950</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.5</v>
+        <v>7.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AD8" t="n">
         <v>950</v>
@@ -2459,7 +2459,7 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>12.5</v>
+        <v>6.8</v>
       </c>
       <c r="AG8" t="n">
         <v>970</v>
@@ -2474,7 +2474,7 @@
         <v>180</v>
       </c>
       <c r="AK8" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AL8" t="n">
         <v>330</v>
@@ -2483,7 +2483,7 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>15</v>
+        <v>6.2</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
@@ -2492,13 +2492,13 @@
         <v>7.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AT8" t="n">
         <v>5.9</v>
@@ -2507,43 +2507,43 @@
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.85</v>
+        <v>5.7</v>
       </c>
       <c r="AY8" t="n">
         <v>7</v>
       </c>
       <c r="AZ8" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BC8" t="n">
         <v>9</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.55</v>
+        <v>5.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.92</v>
+        <v>5.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BI8" t="n">
         <v>3.1</v>
@@ -2552,16 +2552,16 @@
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>3.95</v>
+        <v>6.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BO8" t="n">
         <v>2.84</v>
@@ -2576,35 +2576,35 @@
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.95</v>
+        <v>7.2</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.05</v>
+        <v>6.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-04 01:13:30</t>
+          <t>2026-06-04 03:20:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="H2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I2" t="n">
         <v>4.1</v>
       </c>
-      <c r="I2" t="n">
-        <v>4.5</v>
-      </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
@@ -884,139 +884,139 @@
         <v>3.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P2" t="n">
         <v>1.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R2" t="n">
         <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W2" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="X2" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA2" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG2" t="n">
         <v>10.5</v>
       </c>
       <c r="AH2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN2" t="n">
         <v>23</v>
       </c>
-      <c r="AI2" t="n">
-        <v>190</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>450</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>20</v>
-      </c>
       <c r="AO2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AP2" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AS2" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AX2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BB2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BC2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BD2" t="n">
         <v>38</v>
       </c>
       <c r="BE2" t="n">
-        <v>28</v>
+        <v>12.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="BH2" t="n">
         <v>3.05</v>
@@ -1025,62 +1025,62 @@
         <v>2.6</v>
       </c>
       <c r="BJ2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>17</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
         <v>11</v>
       </c>
-      <c r="BK2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>15</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -1111,52 +1111,52 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="I3" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="R3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T3" t="n">
         <v>1.55</v>
       </c>
-      <c r="S3" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.58</v>
-      </c>
       <c r="U3" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="V3" t="n">
         <v>2.04</v>
@@ -1165,88 +1165,88 @@
         <v>1.29</v>
       </c>
       <c r="X3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA3" t="n">
         <v>23</v>
       </c>
       <c r="AB3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
         <v>11</v>
       </c>
       <c r="AE3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>700</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS3" t="n">
         <v>18.5</v>
       </c>
-      <c r="AF3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>700</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>700</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>700</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>18</v>
-      </c>
       <c r="AT3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AW3" t="n">
         <v>15</v>
       </c>
       <c r="AX3" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ3" t="n">
         <v>14</v>
@@ -1255,31 +1255,31 @@
         <v>22</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="BD3" t="n">
         <v>28</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.4</v>
+        <v>44</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK3" t="n">
         <v>7.6</v>
@@ -1288,25 +1288,25 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BO3" t="n">
         <v>6.6</v>
       </c>
       <c r="BP3" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT3" t="n">
         <v>5.1</v>
@@ -1315,26 +1315,26 @@
         <v>4.2</v>
       </c>
       <c r="BV3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BW3" t="n">
         <v>5.5</v>
       </c>
       <c r="BX3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BY3" t="n">
         <v>6.8</v>
       </c>
       <c r="BZ3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -1365,64 +1365,64 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I4" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K4" t="n">
         <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="Q4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T4" t="n">
         <v>1.55</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.53</v>
-      </c>
       <c r="U4" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="V4" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="Y4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z4" t="n">
         <v>22</v>
@@ -1431,109 +1431,109 @@
         <v>85</v>
       </c>
       <c r="AB4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD4" t="n">
         <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG4" t="n">
         <v>14.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AJ4" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AL4" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
         <v>200</v>
       </c>
       <c r="AN4" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR4" t="n">
         <v>17</v>
       </c>
       <c r="AS4" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="AT4" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AY4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ4" t="n">
         <v>11</v>
       </c>
       <c r="BA4" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BB4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="BC4" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD4" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BF4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BG4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BJ4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK4" t="n">
         <v>4.5</v>
@@ -1542,25 +1542,25 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN4" t="n">
         <v>6.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP4" t="n">
         <v>19.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT4" t="n">
         <v>6.4</v>
@@ -1569,26 +1569,26 @@
         <v>4.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BW4" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="BX4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY4" t="n">
         <v>6.8</v>
       </c>
       <c r="BZ4" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.9</v>
+        <v>12</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -1619,79 +1619,79 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="G5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H5" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I5" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J5" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="L5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M5" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
         <v>1.46</v>
       </c>
       <c r="P5" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="R5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
         <v>4.7</v>
       </c>
       <c r="T5" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U5" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X5" t="n">
-        <v>8.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="AA5" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>44</v>
       </c>
       <c r="AC5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD5" t="n">
-        <v>970</v>
+        <v>100</v>
       </c>
       <c r="AE5" t="n">
         <v>500</v>
@@ -1703,7 +1703,7 @@
         <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AI5" t="n">
         <v>500</v>
@@ -1730,28 +1730,28 @@
         <v>5.1</v>
       </c>
       <c r="AQ5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR5" t="n">
         <v>8.6</v>
       </c>
-      <c r="AR5" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AS5" t="n">
-        <v>17.5</v>
+        <v>7.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AW5" t="n">
         <v>6.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY5" t="n">
         <v>7.6</v>
@@ -1763,19 +1763,19 @@
         <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BC5" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BG5" t="n">
         <v>7.2</v>
@@ -1784,7 +1784,7 @@
         <v>2.98</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
@@ -1796,28 +1796,28 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2.04</v>
+        <v>1.46</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="BT5" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="BU5" t="n">
         <v>3.9</v>
@@ -1826,23 +1826,23 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>2.14</v>
+        <v>3.15</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.23</v>
+        <v>1.48</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>
@@ -1882,10 +1882,10 @@
         <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="J6" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="K6" t="n">
         <v>6.4</v>
@@ -1894,7 +1894,7 @@
         <v>1.41</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
         <v>3.85</v>
@@ -1903,10 +1903,10 @@
         <v>1.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R6" t="n">
         <v>1.35</v>
@@ -1915,10 +1915,10 @@
         <v>3.55</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="V6" t="n">
         <v>1.05</v>
@@ -1927,19 +1927,19 @@
         <v>4.1</v>
       </c>
       <c r="X6" t="n">
-        <v>950</v>
+        <v>19</v>
       </c>
       <c r="Y6" t="n">
         <v>950</v>
       </c>
       <c r="Z6" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AC6" t="n">
         <v>26</v>
@@ -1963,7 +1963,7 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>9.6</v>
+        <v>22</v>
       </c>
       <c r="AK6" t="n">
         <v>34</v>
@@ -1972,28 +1972,28 @@
         <v>330</v>
       </c>
       <c r="AM6" t="n">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="AN6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU6" t="n">
         <v>7.4</v>
@@ -2002,19 +2002,19 @@
         <v>8.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AY6" t="n">
         <v>7</v>
       </c>
       <c r="AZ6" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="BB6" t="n">
         <v>7.8</v>
@@ -2023,22 +2023,22 @@
         <v>9</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE6" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
@@ -2050,13 +2050,13 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BP6" t="n">
         <v>7.6</v>
@@ -2068,7 +2068,7 @@
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
@@ -2086,17 +2086,17 @@
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 05:28:11</t>
+          <t>2026-06-04 07:35:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -860,19 +860,19 @@
         <v>2.08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K2" t="n">
         <v>3.8</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>1.47</v>
@@ -881,19 +881,19 @@
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O2" t="n">
         <v>1.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q2" t="n">
         <v>2.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
         <v>4.2</v>
@@ -902,22 +902,22 @@
         <v>1.9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y2" t="n">
         <v>13</v>
       </c>
-      <c r="Y2" t="n">
-        <v>12.5</v>
-      </c>
       <c r="Z2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA2" t="n">
         <v>90</v>
@@ -926,7 +926,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
         <v>17</v>
@@ -947,10 +947,10 @@
         <v>75</v>
       </c>
       <c r="AJ2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK2" t="n">
         <v>32</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>26</v>
       </c>
       <c r="AL2" t="n">
         <v>46</v>
@@ -959,7 +959,7 @@
         <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AO2" t="n">
         <v>70</v>
@@ -968,10 +968,10 @@
         <v>10.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS2" t="n">
         <v>55</v>
@@ -983,10 +983,10 @@
         <v>7.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AX2" t="n">
         <v>10.5</v>
@@ -1004,83 +1004,83 @@
         <v>24</v>
       </c>
       <c r="BC2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BD2" t="n">
         <v>38</v>
       </c>
       <c r="BE2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF2" t="n">
         <v>17.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO2" t="n">
         <v>4.2</v>
       </c>
       <c r="BP2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
         <v>10.5</v>
       </c>
-      <c r="BT2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>11</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>12</v>
-      </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="I3" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="J3" t="n">
         <v>4.2</v>
@@ -1129,212 +1129,212 @@
         <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="T3" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="U3" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="V3" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="W3" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X3" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="Z3" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB3" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AD3" t="n">
         <v>11</v>
       </c>
       <c r="AE3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF3" t="n">
         <v>100</v>
       </c>
       <c r="AG3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AH3" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AI3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AJ3" t="n">
         <v>700</v>
       </c>
       <c r="AK3" t="n">
-        <v>150</v>
+        <v>44</v>
       </c>
       <c r="AL3" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="AN3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX3" t="n">
         <v>34</v>
       </c>
-      <c r="AO3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>21</v>
-      </c>
       <c r="AY3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ3" t="n">
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BC3" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD3" t="n">
         <v>36</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>28</v>
       </c>
       <c r="BE3" t="n">
         <v>44</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.6</v>
+        <v>25</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BO3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BX3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BY3" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BZ3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="CA3" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
@@ -1365,61 +1365,61 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="I4" t="n">
         <v>2.64</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="R4" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="S4" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="T4" t="n">
         <v>1.55</v>
       </c>
       <c r="U4" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="V4" t="n">
         <v>1.6</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X4" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="Y4" t="n">
         <v>17</v>
@@ -1428,19 +1428,19 @@
         <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AB4" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD4" t="n">
         <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF4" t="n">
         <v>24</v>
@@ -1449,7 +1449,7 @@
         <v>14.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI4" t="n">
         <v>46</v>
@@ -1461,34 +1461,34 @@
         <v>46</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM4" t="n">
         <v>200</v>
       </c>
       <c r="AN4" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
         <v>17</v>
       </c>
       <c r="AS4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV4" t="n">
         <v>10.5</v>
@@ -1506,7 +1506,7 @@
         <v>11</v>
       </c>
       <c r="BA4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BB4" t="n">
         <v>25</v>
@@ -1515,25 +1515,25 @@
         <v>17</v>
       </c>
       <c r="BD4" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE4" t="n">
         <v>23</v>
       </c>
       <c r="BF4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BG4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK4" t="n">
         <v>4.5</v>
@@ -1542,16 +1542,16 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BN4" t="n">
         <v>6.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ4" t="n">
         <v>6.2</v>
@@ -1560,7 +1560,7 @@
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT4" t="n">
         <v>6.4</v>
@@ -1572,23 +1572,23 @@
         <v>18</v>
       </c>
       <c r="BW4" t="n">
-        <v>12.5</v>
+        <v>6.2</v>
       </c>
       <c r="BX4" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
         <v>6.8</v>
       </c>
       <c r="BZ4" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="CA4" t="n">
-        <v>12</v>
+        <v>5.9</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G5" t="n">
         <v>3.45</v>
       </c>
-      <c r="G5" t="n">
-        <v>3.7</v>
-      </c>
       <c r="H5" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="I5" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="J5" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M5" t="n">
         <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="O5" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P5" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="V5" t="n">
         <v>1.57</v>
       </c>
       <c r="W5" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="X5" t="n">
-        <v>17</v>
+        <v>9.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="Z5" t="n">
-        <v>28</v>
+        <v>15.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>40</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="AC5" t="n">
-        <v>16</v>
+        <v>6.8</v>
       </c>
       <c r="AD5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>100</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>900</v>
       </c>
       <c r="AK5" t="n">
         <v>500</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="AO5" t="n">
         <v>600</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="AQ5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT5" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AR5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AU5" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="AX5" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY5" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="BA5" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="BB5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>27</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BU5" t="n">
         <v>4</v>
       </c>
-      <c r="BC5" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>42</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.44</v>
+        <v>3.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.48</v>
+        <v>3.5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G6" t="n">
         <v>1.32</v>
@@ -1882,58 +1882,58 @@
         <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="J6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P6" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S6" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="U6" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="V6" t="n">
         <v>1.05</v>
       </c>
       <c r="W6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="Z6" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
@@ -1942,161 +1942,161 @@
         <v>7.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>950</v>
+        <v>300</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AF6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AG6" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>950</v>
+        <v>160</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22</v>
+        <v>9.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>34</v>
+        <v>16.5</v>
       </c>
       <c r="AL6" t="n">
         <v>330</v>
       </c>
       <c r="AM6" t="n">
-        <v>480</v>
+        <v>430</v>
       </c>
       <c r="AN6" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>14.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.4</v>
+        <v>23</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AY6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9.4</v>
+        <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BN6" t="n">
         <v>3.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="BP6" t="n">
         <v>7.6</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BU6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 07:35:20</t>
+          <t>2026-06-04 09:43:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -857,121 +857,121 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="G2" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="H2" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P2" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="V2" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="X2" t="n">
         <v>12.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AA2" t="n">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC2" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC2" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AD2" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="AF2" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG2" t="n">
         <v>10.5</v>
       </c>
       <c r="AH2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK2" t="n">
         <v>22</v>
       </c>
-      <c r="AI2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>32</v>
-      </c>
       <c r="AL2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
         <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="AO2" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AP2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AS2" t="n">
         <v>55</v>
@@ -980,28 +980,28 @@
         <v>7.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW2" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AX2" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AY2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
@@ -1010,77 +1010,77 @@
         <v>38</v>
       </c>
       <c r="BE2" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BP2" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT2" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -1111,64 +1111,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="G3" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="H3" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="I3" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P3" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="R3" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="T3" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="U3" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="V3" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="X3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z3" t="n">
         <v>16.5</v>
@@ -1177,100 +1177,100 @@
         <v>22</v>
       </c>
       <c r="AB3" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AC3" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH3" t="n">
         <v>17</v>
       </c>
-      <c r="AF3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>15</v>
-      </c>
       <c r="AI3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AJ3" t="n">
-        <v>700</v>
+        <v>90</v>
       </c>
       <c r="AK3" t="n">
         <v>44</v>
       </c>
       <c r="AL3" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="AN3" t="n">
         <v>30</v>
       </c>
       <c r="AO3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AP3" t="n">
         <v>24</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR3" t="n">
         <v>13</v>
       </c>
       <c r="AS3" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AT3" t="n">
         <v>22</v>
       </c>
       <c r="AU3" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AW3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>14</v>
       </c>
       <c r="BA3" t="n">
         <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BC3" t="n">
         <v>34</v>
       </c>
       <c r="BD3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE3" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="BF3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH3" t="n">
         <v>5.1</v>
@@ -1279,7 +1279,7 @@
         <v>4.1</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK3" t="n">
         <v>7.2</v>
@@ -1291,13 +1291,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BN3" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BO3" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ3" t="n">
         <v>7</v>
@@ -1309,16 +1309,16 @@
         <v>7.2</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BX3" t="n">
         <v>21</v>
@@ -1327,14 +1327,14 @@
         <v>6.4</v>
       </c>
       <c r="BZ3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -1365,136 +1365,136 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="G4" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="H4" t="n">
         <v>2.44</v>
       </c>
       <c r="I4" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="O4" t="n">
         <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="Q4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T4" t="n">
         <v>1.56</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.55</v>
-      </c>
       <c r="U4" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Y4" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA4" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AB4" t="n">
         <v>21</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AF4" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AG4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH4" t="n">
         <v>14</v>
       </c>
       <c r="AI4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ4" t="n">
         <v>100</v>
       </c>
       <c r="AK4" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="AL4" t="n">
         <v>50</v>
       </c>
       <c r="AM4" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AN4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT4" t="n">
         <v>16.5</v>
       </c>
-      <c r="AO4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>16</v>
-      </c>
       <c r="AU4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV4" t="n">
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AX4" t="n">
         <v>19</v>
@@ -1506,37 +1506,37 @@
         <v>11</v>
       </c>
       <c r="BA4" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BB4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="BC4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
         <v>20</v>
       </c>
       <c r="BE4" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BF4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1548,13 +1548,13 @@
         <v>6.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BP4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
@@ -1566,10 +1566,10 @@
         <v>6.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BW4" t="n">
         <v>6.2</v>
@@ -1584,11 +1584,11 @@
         <v>16</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -1619,64 +1619,64 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="G5" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="H5" t="n">
-        <v>2.68</v>
+        <v>2.48</v>
       </c>
       <c r="I5" t="n">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
         <v>3.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M5" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
         <v>1.48</v>
       </c>
       <c r="P5" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="R5" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T5" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="U5" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="V5" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="W5" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="X5" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z5" t="n">
         <v>15.5</v>
@@ -1685,79 +1685,79 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG5" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="AK5" t="n">
         <v>500</v>
       </c>
       <c r="AL5" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AO5" t="n">
-        <v>600</v>
+        <v>32</v>
       </c>
       <c r="AP5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS5" t="n">
-        <v>30</v>
+        <v>17.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>16.5</v>
+        <v>24</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="AY5" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="BA5" t="n">
         <v>30</v>
@@ -1766,28 +1766,28 @@
         <v>32</v>
       </c>
       <c r="BC5" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="BD5" t="n">
-        <v>13.5</v>
+        <v>40</v>
       </c>
       <c r="BE5" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK5" t="n">
         <v>6.4</v>
@@ -1796,10 +1796,10 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO5" t="n">
         <v>4.8</v>
@@ -1808,41 +1808,41 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.8</v>
+        <v>2.18</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>3.6</v>
+        <v>1.49</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>3.7</v>
+        <v>9</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.5</v>
+        <v>1.55</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.5</v>
+        <v>1.61</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>
@@ -1876,16 +1876,16 @@
         <v>1.29</v>
       </c>
       <c r="G6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="H6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I6" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="J6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="K6" t="n">
         <v>6.2</v>
@@ -1915,22 +1915,22 @@
         <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="U6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="V6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="X6" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y6" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="Z6" t="n">
         <v>180</v>
@@ -1945,28 +1945,28 @@
         <v>19.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>300</v>
+        <v>950</v>
       </c>
       <c r="AE6" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="AF6" t="n">
         <v>7</v>
       </c>
       <c r="AG6" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AI6" t="n">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="AJ6" t="n">
         <v>9.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL6" t="n">
         <v>330</v>
@@ -1975,7 +1975,7 @@
         <v>430</v>
       </c>
       <c r="AN6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1987,10 +1987,10 @@
         <v>14.5</v>
       </c>
       <c r="AR6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS6" t="n">
         <v>11</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>11.5</v>
       </c>
       <c r="AT6" t="n">
         <v>6.2</v>
@@ -2002,37 +2002,37 @@
         <v>23</v>
       </c>
       <c r="AW6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AX6" t="n">
         <v>6</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC6" t="n">
         <v>14</v>
       </c>
       <c r="BD6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>11.5</v>
+        <v>130</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH6" t="n">
         <v>3.8</v>
@@ -2044,34 +2044,34 @@
         <v>15</v>
       </c>
       <c r="BK6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="BN6" t="n">
         <v>3.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BP6" t="n">
         <v>7.6</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BU6" t="n">
         <v>7.6</v>
@@ -2086,7 +2086,7 @@
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ6" t="n">
         <v>14</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 09:43:16</t>
+          <t>2026-06-04 11:52:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.91</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>1.95</v>
+        <v>9.4</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3</v>
+        <v>1.56</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>1.58</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="R2" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="S2" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="T2" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="U2" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.27</v>
+        <v>2.72</v>
       </c>
       <c r="W2" t="n">
-        <v>2.04</v>
+        <v>1.12</v>
       </c>
       <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>430</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>280</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY2" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE2" t="n">
+      <c r="AZ2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>180</v>
+      </c>
+      <c r="BF2" t="n">
         <v>95</v>
       </c>
-      <c r="AF2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BG2" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="I3" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="P3" t="n">
-        <v>2.66</v>
+        <v>2.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="S3" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="U3" t="n">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="V3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Y3" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="Z3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AB3" t="n">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="AC3" t="n">
         <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AG3" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AI3" t="n">
         <v>26</v>
       </c>
       <c r="AJ3" t="n">
-        <v>90</v>
+        <v>700</v>
       </c>
       <c r="AK3" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AL3" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM3" t="n">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="AN3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AO3" t="n">
         <v>8.6</v>
       </c>
       <c r="AP3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AT3" t="n">
         <v>22</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV3" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AX3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AY3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA3" t="n">
         <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BC3" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BD3" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BE3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BF3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BG3" t="n">
         <v>7.4</v>
       </c>
       <c r="BH3" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK3" t="n">
         <v>7.2</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BN3" t="n">
         <v>8</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BP3" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BT3" t="n">
         <v>5.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BV3" t="n">
         <v>12.5</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BX3" t="n">
         <v>21</v>
       </c>
       <c r="BY3" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -1365,85 +1365,85 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="G4" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="H4" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="I4" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="P4" t="n">
-        <v>2.68</v>
+        <v>2.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="R4" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="U4" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V4" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W4" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="X4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Y4" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="Z4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AB4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC4" t="n">
         <v>10.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="AF4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG4" t="n">
         <v>14</v>
@@ -1452,143 +1452,143 @@
         <v>14</v>
       </c>
       <c r="AI4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ4" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AK4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM4" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
         <v>15.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AP4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV4" t="n">
         <v>10.5</v>
       </c>
       <c r="AW4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX4" t="n">
         <v>19.5</v>
       </c>
-      <c r="AX4" t="n">
-        <v>19</v>
-      </c>
       <c r="AY4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BB4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="BC4" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD4" t="n">
         <v>21</v>
       </c>
-      <c r="BD4" t="n">
-        <v>20</v>
-      </c>
       <c r="BE4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BF4" t="n">
         <v>12.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BJ4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN4" t="n">
         <v>6.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV4" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CA4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -1622,19 +1622,19 @@
         <v>3.45</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H5" t="n">
         <v>2.48</v>
       </c>
       <c r="I5" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L5" t="n">
         <v>1.53</v>
@@ -1646,28 +1646,28 @@
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P5" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T5" t="n">
         <v>1.9</v>
       </c>
       <c r="U5" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="V5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W5" t="n">
         <v>1.37</v>
@@ -1676,16 +1676,16 @@
         <v>10.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="Z5" t="n">
         <v>15.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AC5" t="n">
         <v>7</v>
@@ -1694,49 +1694,49 @@
         <v>13</v>
       </c>
       <c r="AE5" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AF5" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AG5" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI5" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
         <v>170</v>
       </c>
       <c r="AK5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL5" t="n">
         <v>500</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>110</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO5" t="n">
         <v>32</v>
       </c>
       <c r="AP5" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS5" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AT5" t="n">
         <v>9</v>
@@ -1748,101 +1748,101 @@
         <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AX5" t="n">
         <v>20</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="AZ5" t="n">
         <v>12.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="BB5" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BC5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BD5" t="n">
         <v>40</v>
       </c>
       <c r="BE5" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="BJ5" t="n">
         <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="BN5" t="n">
         <v>6.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2.18</v>
+        <v>1.57</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="BT5" t="n">
         <v>5.1</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>
@@ -1873,97 +1873,97 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="G6" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="H6" t="n">
         <v>15</v>
       </c>
       <c r="I6" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="J6" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="K6" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>1.31</v>
       </c>
       <c r="P6" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T6" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="U6" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="V6" t="n">
         <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="X6" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Y6" t="n">
         <v>85</v>
       </c>
       <c r="Z6" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="AD6" t="n">
         <v>950</v>
       </c>
       <c r="AE6" t="n">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="AF6" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AG6" t="n">
         <v>15.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AI6" t="n">
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="AJ6" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK6" t="n">
         <v>17</v>
@@ -1975,25 +1975,25 @@
         <v>430</v>
       </c>
       <c r="AN6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>14.5</v>
       </c>
       <c r="AR6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS6" t="n">
         <v>10.5</v>
       </c>
-      <c r="AS6" t="n">
-        <v>11</v>
-      </c>
       <c r="AT6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU6" t="n">
         <v>10.5</v>
@@ -2002,49 +2002,49 @@
         <v>23</v>
       </c>
       <c r="AW6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX6" t="n">
         <v>6</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BC6" t="n">
         <v>14</v>
       </c>
       <c r="BD6" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE6" t="n">
         <v>130</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH6" t="n">
         <v>3.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2053,50 +2053,50 @@
         <v>160</v>
       </c>
       <c r="BN6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="BP6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="BR6" t="n">
         <v>30</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>14</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-04 11:52:00</t>
+          <t>2026-06-04 14:01:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,180 +843,180 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ES Ben Aknoun</t>
+          <t>AFC Eskilstuna</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Karlbergs BK</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>1.28</v>
       </c>
       <c r="G2" t="n">
-        <v>9.4</v>
+        <v>1.31</v>
       </c>
       <c r="H2" t="n">
-        <v>1.56</v>
+        <v>29</v>
       </c>
       <c r="I2" t="n">
-        <v>1.58</v>
+        <v>48</v>
       </c>
       <c r="J2" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="K2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W2" t="n">
         <v>3.95</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.12</v>
-      </c>
       <c r="X2" t="n">
         <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>930</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
         <v>7</v>
       </c>
-      <c r="AA2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>75</v>
-      </c>
       <c r="AL2" t="n">
-        <v>130</v>
+        <v>24</v>
       </c>
       <c r="AM2" t="n">
-        <v>430</v>
+        <v>220</v>
       </c>
       <c r="AN2" t="n">
-        <v>280</v>
+        <v>48</v>
       </c>
       <c r="AO2" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.2</v>
+        <v>220</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.4</v>
+        <v>220</v>
       </c>
       <c r="AS2" t="n">
-        <v>19.5</v>
+        <v>220</v>
       </c>
       <c r="AT2" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.9</v>
+        <v>25</v>
       </c>
       <c r="AV2" t="n">
-        <v>7.4</v>
+        <v>25</v>
       </c>
       <c r="AW2" t="n">
         <v>25</v>
       </c>
       <c r="AX2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>85</v>
+      </c>
+      <c r="BF2" t="n">
         <v>17</v>
       </c>
-      <c r="AY2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>50</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>70</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>180</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>95</v>
-      </c>
       <c r="BG2" t="n">
-        <v>32</v>
+        <v>160</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Laholms</t>
+          <t>HUSA Agadir</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hassleholms IF</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>2.96</v>
       </c>
       <c r="H3" t="n">
-        <v>1.94</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>2.02</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="S3" t="n">
+        <v>29</v>
+      </c>
+      <c r="T3" t="n">
         <v>4.1</v>
       </c>
-      <c r="K3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N3" t="n">
-        <v>7</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="U3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.5</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.33</v>
-      </c>
       <c r="X3" t="n">
-        <v>36</v>
+        <v>3.65</v>
       </c>
       <c r="Y3" t="n">
-        <v>18</v>
+        <v>7.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="AA3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>270</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>530</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>280</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR3" t="n">
         <v>24</v>
       </c>
-      <c r="AB3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>700</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM3" t="n">
+      <c r="AS3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>65</v>
       </c>
-      <c r="AN3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ3" t="n">
+      <c r="BA3" t="n">
+        <v>250</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>60</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>90</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>290</v>
+      </c>
+      <c r="BE3" t="n">
         <v>12.5</v>
       </c>
-      <c r="BA3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>55</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>38</v>
-      </c>
       <c r="BF3" t="n">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.4</v>
+        <v>310</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,752 +1351,244 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AFC Eskilstuna</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Karlbergs BK</t>
+          <t>DHJ El Jadida</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.72</v>
+        <v>1.29</v>
       </c>
       <c r="G4" t="n">
-        <v>2.98</v>
+        <v>1.3</v>
       </c>
       <c r="H4" t="n">
-        <v>2.48</v>
+        <v>15</v>
       </c>
       <c r="I4" t="n">
-        <v>2.62</v>
+        <v>18.5</v>
       </c>
       <c r="J4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>180</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>160</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>450</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>340</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>430</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>30</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>130</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH4" t="n">
         <v>3.85</v>
       </c>
-      <c r="K4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N4" t="n">
-        <v>7</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X4" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR4" t="n">
+      <c r="BI4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>160</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT4" t="n">
         <v>17.5</v>
       </c>
-      <c r="AS4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT4" t="n">
+      <c r="BU4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ4" t="n">
         <v>16</v>
       </c>
-      <c r="AU4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>23</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>18</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>15</v>
-      </c>
       <c r="CA4" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-04 14:01:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Moroccan Botola Pro 1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>15:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>HUSA Agadir</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>FUS Rabat</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>170</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>36</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>26</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>2026-06-04 14:01:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Moroccan Botola Pro 1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>17:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>FAR Rabat</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>DHJ El Jadida</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="H6" t="n">
-        <v>15</v>
-      </c>
-      <c r="I6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="X6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>85</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>170</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>380</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>280</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>330</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>430</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>130</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>160</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>30</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>14</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-06-04 14:01:32</t>
+          <t>2026-06-04 16:10:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,180 +843,180 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AFC Eskilstuna</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Karlbergs BK</t>
+          <t>DHJ El Jadida</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="G2" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="H2" t="n">
+        <v>55</v>
+      </c>
+      <c r="I2" t="n">
+        <v>70</v>
+      </c>
+      <c r="J2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="S2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>870</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK2" t="n">
         <v>29</v>
       </c>
-      <c r="I2" t="n">
-        <v>48</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>930</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>7</v>
-      </c>
       <c r="AL2" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AR2" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AS2" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AT2" t="n">
-        <v>25</v>
+        <v>3.45</v>
       </c>
       <c r="AU2" t="n">
-        <v>25</v>
+        <v>8.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="AW2" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="AX2" t="n">
-        <v>25</v>
+        <v>3.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.74</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.8</v>
+        <v>50</v>
       </c>
       <c r="BA2" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="BB2" t="n">
-        <v>25</v>
+        <v>7.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="BD2" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="BE2" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="BF2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>160</v>
+        <v>29</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1080,515 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-04 16:10:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Moroccan Botola Pro 1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>15:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>HUSA Agadir</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FUS Rabat</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="S3" t="n">
-        <v>29</v>
-      </c>
-      <c r="T3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>270</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>95</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>140</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>530</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>280</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>65</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>250</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>60</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>90</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>290</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>150</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>310</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>2026-06-04 16:10:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Moroccan Botola Pro 1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>17:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>FAR Rabat</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>DHJ El Jadida</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>15</v>
-      </c>
-      <c r="I4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="K4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="X4" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>180</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>160</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>450</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>340</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>430</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>30</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>130</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>15</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>160</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>16</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>2026-06-04 16:10:43</t>
+          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -827,260 +827,6 @@
       <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Moroccan Botola Pro 1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>17:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>FAR Rabat</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>DHJ El Jadida</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="H2" t="n">
-        <v>55</v>
-      </c>
-      <c r="I2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="K2" t="n">
-        <v>11</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="S2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>870</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>50</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>120</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>29</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>2026-06-04 18:19:43</t>
         </is>
       </c>
     </row>
